--- a/Data/Results/System/Pair_Index.xlsx
+++ b/Data/Results/System/Pair_Index.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Pair Index" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pair Index'!$A$1:$AQ$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Pair Index'!$A$1:$AQ$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -46,16 +49,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="00DDEBF7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DDEBF7"/>
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -63,13 +66,19 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -439,16 +448,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AQ19"/>
+  <dimension ref="A1:AQ39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
     <col width="33" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="38" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
     <col width="22" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
@@ -457,10 +466,10 @@
     <col width="48" customWidth="1" min="13" max="13"/>
     <col width="27" customWidth="1" min="14" max="14"/>
     <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="28" customWidth="1" min="16" max="16"/>
-    <col width="28" customWidth="1" min="17" max="17"/>
-    <col width="29" customWidth="1" min="18" max="18"/>
-    <col width="28" customWidth="1" min="19" max="19"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="31" customWidth="1" min="17" max="17"/>
+    <col width="31" customWidth="1" min="18" max="18"/>
+    <col width="31" customWidth="1" min="19" max="19"/>
     <col width="34" customWidth="1" min="20" max="20"/>
     <col width="35" customWidth="1" min="21" max="21"/>
     <col width="32" customWidth="1" min="22" max="22"/>
@@ -476,8 +485,8 @@
     <col width="29" customWidth="1" min="32" max="32"/>
     <col width="48" customWidth="1" min="33" max="33"/>
     <col width="28" customWidth="1" min="34" max="34"/>
-    <col width="47" customWidth="1" min="35" max="35"/>
-    <col width="40" customWidth="1" min="36" max="36"/>
+    <col width="48" customWidth="1" min="35" max="35"/>
+    <col width="48" customWidth="1" min="36" max="36"/>
     <col width="34" customWidth="1" min="37" max="37"/>
     <col width="25" customWidth="1" min="38" max="38"/>
     <col width="26" customWidth="1" min="39" max="39"/>
@@ -712,22 +721,22 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>CAND_007</t>
+          <t>CAND_036</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>SilkBoard to Madhuravoyal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -737,7 +746,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>PASSED_WITH_SPARSE_TELEMETRY</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -747,73 +756,73 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>05-07-2026</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>29-07-2026</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>15-07-2026</t>
+          <t>05-07-2026_to_29-07-2026</t>
         </is>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_001_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_29-07-2026\PAIR_001_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
-          <t>verified_3c60b16f324a86f6</t>
+          <t>verified_f3166bdf5ada7690</t>
         </is>
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>verified_c56ab71649575f28</t>
+          <t>verified_885e07a3434192f0</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 09:22:41.344488</t>
+          <t>2026-07-05 12:00:06.054858704</t>
         </is>
       </c>
       <c r="Q2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 13:23:07.961613</t>
+          <t>2026-07-05 13:38:16.188122931</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 11:20:23.000000</t>
+          <t>2026-07-30 01:54:40.897841973</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>2026-07-15 15:54:44.000000</t>
+          <t>2026-07-30 03:20:13.585700204</t>
         </is>
       </c>
       <c r="T2" s="2" t="n">
-        <v>148.1987690237779</v>
+        <v>102.5403079815419</v>
       </c>
       <c r="U2" s="2" t="n">
-        <v>148.1254196841037</v>
+        <v>102.5404226319266</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0.0733493396741096</v>
+        <v>0.0001146503847166</v>
       </c>
       <c r="W2" s="2" t="n">
-        <v>0.04951840125114</v>
+        <v>0.0001118100647184</v>
       </c>
       <c r="X2" s="2" t="n">
-        <v>2.962508393682075</v>
+        <v>2.050806159630838</v>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
@@ -821,25 +830,25 @@
         </is>
       </c>
       <c r="Z2" s="2" t="n">
-        <v>148.1187897046324</v>
+        <v>102.4541106733238</v>
       </c>
       <c r="AA2" s="2" t="n">
-        <v>0.9985272459499264</v>
+        <v>0.9246031746031746</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1</v>
+        <v>0.3355570380253501</v>
       </c>
       <c r="AC2" s="2" t="n">
-        <v>13.03198481424892</v>
+        <v>12.83029416621557</v>
       </c>
       <c r="AD2" s="2" t="n">
-        <v>80.21124616979466</v>
+        <v>78.77727067632964</v>
       </c>
       <c r="AE2" s="2" t="n">
-        <v>11.9387286487001</v>
+        <v>12.87248999333421</v>
       </c>
       <c r="AF2" s="2" t="n">
-        <v>79.80808923032174</v>
+        <v>79.66046510643602</v>
       </c>
       <c r="AG2" s="2" t="inlineStr">
         <is>
@@ -853,398 +862,398 @@
       </c>
       <c r="AI2" s="2" t="inlineStr">
         <is>
-          <t>PAIR_001 | STRICT | Chennai to Pondicherry</t>
+          <t>PAIR_001 | NONSTRICT | SilkBoard to Madhuravoyal</t>
         </is>
       </c>
       <c r="AJ2" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK2" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026 17:50:46</t>
+          <t>29-09-2026 12:15:18</t>
         </is>
       </c>
       <c r="AL2" s="2" t="n">
-        <v>1180</v>
+        <v>1058</v>
       </c>
       <c r="AM2" s="2" t="n">
-        <v>591</v>
+        <v>841</v>
       </c>
       <c r="AN2" s="2" t="n">
-        <v>14426.618</v>
+        <v>5890.133</v>
       </c>
       <c r="AO2" s="2" t="n">
-        <v>16461</v>
+        <v>5132.688</v>
       </c>
       <c r="AP2" s="2" t="n">
-        <v>148198.7690237775</v>
+        <v>102540.3079815431</v>
       </c>
       <c r="AQ2" s="2" t="n">
-        <v>148125.4196841063</v>
+        <v>102540.4226319246</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>PAIR_002</t>
         </is>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>CAND_008</t>
-        </is>
-      </c>
-      <c r="D3" s="3" t="inlineStr">
-        <is>
-          <t>Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>CAND_040</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
-        <is>
-          <t>PASSED_WITH_SPARSE_TELEMETRY</t>
-        </is>
-      </c>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I3" s="3" t="inlineStr">
-        <is>
-          <t>15-07-2026</t>
-        </is>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>15-07-2026_to_17-07-2026</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="M3" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_002_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="N3" s="3" t="inlineStr">
-        <is>
-          <t>verified_3c60b16f324a86f6</t>
-        </is>
-      </c>
-      <c r="O3" s="3" t="inlineStr">
-        <is>
-          <t>verified_af2997304a2169c1</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 09:56:19.501798</t>
-        </is>
-      </c>
-      <c r="Q3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 13:25:55.017121</t>
-        </is>
-      </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 11:43:51.000000</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 15:25:00.000000</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="n">
-        <v>141.622003133759</v>
-      </c>
-      <c r="U3" s="3" t="n">
-        <v>141.6711046862735</v>
-      </c>
-      <c r="V3" s="3" t="n">
-        <v>0.0491015525145144</v>
-      </c>
-      <c r="W3" s="3" t="n">
-        <v>0.0346708501701808</v>
-      </c>
-      <c r="X3" s="3" t="n">
-        <v>2.832440062675181</v>
-      </c>
-      <c r="Y3" s="3" t="inlineStr">
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>05-07-2026</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>05-07-2026_to_05-09-2026</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-07-2026_to_05-09-2026\PAIR_002_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>verified_f3166bdf5ada7690</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>verified_446af55348030fd8</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:30:40.805999161</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-05 12:55:57.057844736</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 02:39:21.899025883</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 02:59:42.491796168</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>27.18076401749451</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>27.29386365784349</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.1130996403489845</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.4161017706352536</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>0.5436152803498902</v>
+      </c>
+      <c r="Y3" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z3" s="3" t="n">
-        <v>141.6377285485467</v>
-      </c>
-      <c r="AA3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="3" t="n">
-        <v>13.00716498201259</v>
-      </c>
-      <c r="AD3" s="3" t="n">
-        <v>80.23866508993706</v>
-      </c>
-      <c r="AE3" s="3" t="n">
-        <v>11.93203161103106</v>
-      </c>
-      <c r="AF3" s="3" t="n">
-        <v>79.80775894691541</v>
-      </c>
-      <c r="AG3" s="3" t="inlineStr">
+      <c r="Z3" s="2" t="n">
+        <v>27.09025192753889</v>
+      </c>
+      <c r="AA3" s="2" t="n">
+        <v>0.9552238805970148</v>
+      </c>
+      <c r="AB3" s="2" t="n">
+        <v>0.08872581721147429</v>
+      </c>
+      <c r="AC3" s="2" t="n">
+        <v>12.92253801240305</v>
+      </c>
+      <c r="AD3" s="2" t="n">
+        <v>79.10707273364875</v>
+      </c>
+      <c r="AE3" s="2" t="n">
+        <v>12.92007461569218</v>
+      </c>
+      <c r="AF3" s="2" t="n">
+        <v>79.33666986293481</v>
+      </c>
+      <c r="AG3" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH3" s="3" t="inlineStr">
+      <c r="AH3" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI3" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_002 | NONSTRICT | Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="AJ3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK3" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:50:50</t>
-        </is>
-      </c>
-      <c r="AL3" s="3" t="n">
-        <v>1094</v>
-      </c>
-      <c r="AM3" s="3" t="n">
-        <v>1024</v>
-      </c>
-      <c r="AN3" s="3" t="n">
-        <v>12575.515</v>
-      </c>
-      <c r="AO3" s="3" t="n">
-        <v>13269</v>
-      </c>
-      <c r="AP3" s="3" t="n">
-        <v>141622.00313376</v>
-      </c>
-      <c r="AQ3" s="3" t="n">
-        <v>141671.1046862772</v>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_002 | NONSTRICT | SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:18</t>
+        </is>
+      </c>
+      <c r="AL3" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="AM3" s="2" t="n">
+        <v>261</v>
+      </c>
+      <c r="AN3" s="2" t="n">
+        <v>1516.252</v>
+      </c>
+      <c r="AO3" s="2" t="n">
+        <v>1220.593</v>
+      </c>
+      <c r="AP3" s="2" t="n">
+        <v>27180.76401749681</v>
+      </c>
+      <c r="AQ3" s="2" t="n">
+        <v>27293.8636578444</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>PAIR_003</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>CAND_004</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>CAND_015</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to SilkBoard</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026</t>
-        </is>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>15-07-2026</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>15-07-2026_to_17-07-2026</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="M4" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_003_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t>verified_7c397965c0f14f48</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
-        <is>
-          <t>verified_c56ab71649575f28</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 07:51:32.508934</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 11:33:03.533645</t>
-        </is>
-      </c>
-      <c r="R4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 11:20:23.000000</t>
-        </is>
-      </c>
-      <c r="S4" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 15:54:44.000000</t>
-        </is>
-      </c>
-      <c r="T4" s="3" t="n">
-        <v>148.2084119453301</v>
-      </c>
-      <c r="U4" s="3" t="n">
-        <v>148.1502195739105</v>
-      </c>
-      <c r="V4" s="3" t="n">
-        <v>0.0581923714196079</v>
-      </c>
-      <c r="W4" s="3" t="n">
-        <v>0.0392793015001752</v>
-      </c>
-      <c r="X4" s="3" t="n">
-        <v>2.96300439147821</v>
-      </c>
-      <c r="Y4" s="3" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>10-07-2026</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10-07-2026_to_31-07-2026</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\10-07-2026_to_31-07-2026\PAIR_003_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>verified_76d67375faeac508</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>verified_f8d0549d30ce15f8</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 04:34:49.696923265</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-10 04:53:30.372540649</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:13:12.841686638</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 03:42:52.232355039</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="n">
+        <v>11.42391390088956</v>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>11.63657856259252</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0.2126646617029592</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>1.861574444170132</v>
+      </c>
+      <c r="X4" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y4" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z4" s="3" t="n">
-        <v>148.1187897046324</v>
-      </c>
-      <c r="AA4" s="3" t="n">
-        <v>0.9979108635097492</v>
-      </c>
-      <c r="AB4" s="3" t="n">
+      <c r="Z4" s="2" t="n">
+        <v>11.32546086558653</v>
+      </c>
+      <c r="AA4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AC4" s="3" t="n">
-        <v>13.03202304255905</v>
-      </c>
-      <c r="AD4" s="3" t="n">
-        <v>80.21127683194683</v>
-      </c>
-      <c r="AE4" s="3" t="n">
-        <v>11.938534510264</v>
-      </c>
-      <c r="AF4" s="3" t="n">
-        <v>79.80805779812951</v>
-      </c>
-      <c r="AG4" s="3" t="inlineStr">
+      <c r="AB4" s="2" t="n">
+        <v>0.0353569046030686</v>
+      </c>
+      <c r="AC4" s="2" t="n">
+        <v>12.5183245440943</v>
+      </c>
+      <c r="AD4" s="2" t="n">
+        <v>78.23096395316449</v>
+      </c>
+      <c r="AE4" s="2" t="n">
+        <v>12.57504909795723</v>
+      </c>
+      <c r="AF4" s="2" t="n">
+        <v>78.1682685470263</v>
+      </c>
+      <c r="AG4" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH4" s="3" t="inlineStr">
+      <c r="AH4" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI4" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_003 | NONSTRICT | Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="AJ4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:50:53</t>
-        </is>
-      </c>
-      <c r="AL4" s="3" t="n">
-        <v>1155</v>
-      </c>
-      <c r="AM4" s="3" t="n">
-        <v>591</v>
-      </c>
-      <c r="AN4" s="3" t="n">
-        <v>13291.025</v>
-      </c>
-      <c r="AO4" s="3" t="n">
-        <v>16461</v>
-      </c>
-      <c r="AP4" s="3" t="n">
-        <v>148208.411945328</v>
-      </c>
-      <c r="AQ4" s="3" t="n">
-        <v>148150.219573912</v>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_003 | NONSTRICT | Madhuravoyal to SilkBoard</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:18</t>
+        </is>
+      </c>
+      <c r="AL4" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="AN4" s="2" t="n">
+        <v>1120.676</v>
+      </c>
+      <c r="AO4" s="2" t="n">
+        <v>1779.39</v>
+      </c>
+      <c r="AP4" s="2" t="n">
+        <v>11423.91390088975</v>
+      </c>
+      <c r="AQ4" s="2" t="n">
+        <v>11636.57856259103</v>
       </c>
     </row>
     <row r="5">
@@ -1255,12 +1264,12 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>CAND_009</t>
+          <t>CAND_003</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
@@ -1270,7 +1279,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -1280,7 +1289,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>PASSED_WITH_SPARSE_TELEMETRY</t>
+          <t>PASSED_WITH_SPARSE_TELEMETRY_WARNING</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -1295,68 +1304,68 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>15-07-2026_to_19-07-2026</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_004_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026\PAIR_004_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>verified_3c60b16f324a86f6</t>
+          <t>verified_99ae97f04e26ba5b</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>verified_49abd2a79268e808</t>
+          <t>verified_241aada409fad48e</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 09:38:15.771280</t>
+          <t>2026-07-15 09:22:41.344488111</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-15 13:31:09.265001</t>
+          <t>2026-07-15 13:23:07.961613042</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19 11:08:45.000000</t>
+          <t>2026-07-15 11:20:23.000000000</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t>2026-07-19 15:37:58.000000</t>
+          <t>2026-07-15 15:54:44.000000000</t>
         </is>
       </c>
       <c r="T5" s="3" t="n">
-        <v>146.1103622297153</v>
+        <v>148.1987690237779</v>
       </c>
       <c r="U5" s="3" t="n">
-        <v>146.1941703909384</v>
+        <v>148.1254196841037</v>
       </c>
       <c r="V5" s="3" t="n">
-        <v>0.08380816122317469</v>
+        <v>0.0733493396741096</v>
       </c>
       <c r="W5" s="3" t="n">
-        <v>0.0573594917870446</v>
+        <v>0.04951840125114</v>
       </c>
       <c r="X5" s="3" t="n">
-        <v>2.922207244594305</v>
+        <v>2.962508393682075</v>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
@@ -1364,25 +1373,25 @@
         </is>
       </c>
       <c r="Z5" s="3" t="n">
-        <v>146.1331428606738</v>
+        <v>148.1187897046324</v>
       </c>
       <c r="AA5" s="3" t="n">
+        <v>0.9985272459499264</v>
+      </c>
+      <c r="AB5" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="AB5" s="3" t="n">
-        <v>0.9997581089427278</v>
-      </c>
       <c r="AC5" s="3" t="n">
-        <v>13.00874734835186</v>
+        <v>13.03198481424892</v>
       </c>
       <c r="AD5" s="3" t="n">
-        <v>80.21068754867539</v>
+        <v>80.21124616979466</v>
       </c>
       <c r="AE5" s="3" t="n">
-        <v>11.93232918472765</v>
+        <v>11.9387286487001</v>
       </c>
       <c r="AF5" s="3" t="n">
-        <v>79.81457511188292</v>
+        <v>79.80808923032174</v>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
@@ -1396,217 +1405,217 @@
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>PAIR_004 | NONSTRICT | Chennai to Pondicherry</t>
+          <t>PAIR_004 | STRICT | Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK5" s="3" t="inlineStr">
         <is>
-          <t>13-09-2026 17:50:56</t>
+          <t>29-09-2026 12:15:18</t>
         </is>
       </c>
       <c r="AL5" s="3" t="n">
-        <v>1160</v>
+        <v>1180</v>
       </c>
       <c r="AM5" s="3" t="n">
-        <v>1116</v>
+        <v>591</v>
       </c>
       <c r="AN5" s="3" t="n">
-        <v>13973.494</v>
+        <v>14426.618</v>
       </c>
       <c r="AO5" s="3" t="n">
-        <v>16153</v>
+        <v>16461</v>
       </c>
       <c r="AP5" s="3" t="n">
-        <v>146110.3622297162</v>
+        <v>148198.7690237775</v>
       </c>
       <c r="AQ5" s="3" t="n">
-        <v>146194.1703909393</v>
+        <v>148125.4196841063</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>PAIR_005</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C6" s="3" t="inlineStr">
-        <is>
-          <t>CAND_006</t>
-        </is>
-      </c>
-      <c r="D6" s="3" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>CAND_011</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Chennai to Pondicherry</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="H6" s="3" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_WITH_SPARSE_TELEMETRY_WARNING</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>19-07-2026</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>15-07-2026</t>
         </is>
       </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>15-07-2026_to_19-07-2026</t>
-        </is>
-      </c>
-      <c r="L6" s="3" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026_to_17-07-2026</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="N6" s="3" t="inlineStr">
-        <is>
-          <t>verified_bdff61acc7fcadf8</t>
-        </is>
-      </c>
-      <c r="O6" s="3" t="inlineStr">
-        <is>
-          <t>verified_c56ab71649575f28</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 09:10:36.000000</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 12:30:22.807910</t>
-        </is>
-      </c>
-      <c r="R6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 11:22:01.474402</t>
-        </is>
-      </c>
-      <c r="S6" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-15 15:54:44.000000</t>
-        </is>
-      </c>
-      <c r="T6" s="3" t="n">
-        <v>147.8063808897641</v>
-      </c>
-      <c r="U6" s="3" t="n">
-        <v>147.7347082243845</v>
-      </c>
-      <c r="V6" s="3" t="n">
-        <v>0.07167266537959439</v>
-      </c>
-      <c r="W6" s="3" t="n">
-        <v>0.0485144393223667</v>
-      </c>
-      <c r="X6" s="3" t="n">
-        <v>2.954694164487689</v>
-      </c>
-      <c r="Y6" s="3" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_005_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>verified_99ae97f04e26ba5b</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>verified_1ce33d8c8868f78e</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:56:19.501798741</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:25:55.017121045</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:43:51.000000000</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:25:00.000000000</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="n">
+        <v>141.622003133759</v>
+      </c>
+      <c r="U6" s="2" t="n">
+        <v>141.6711046862735</v>
+      </c>
+      <c r="V6" s="2" t="n">
+        <v>0.0491015525145144</v>
+      </c>
+      <c r="W6" s="2" t="n">
+        <v>0.0346708501701808</v>
+      </c>
+      <c r="X6" s="2" t="n">
+        <v>2.832440062675181</v>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z6" s="3" t="n">
-        <v>147.7235427674619</v>
-      </c>
-      <c r="AA6" s="3" t="n">
-        <v>0.9993270524899058</v>
-      </c>
-      <c r="AB6" s="3" t="n">
-        <v>0.9973315543695797</v>
-      </c>
-      <c r="AC6" s="3" t="n">
-        <v>13.03021900769515</v>
-      </c>
-      <c r="AD6" s="3" t="n">
-        <v>80.20912883276921</v>
-      </c>
-      <c r="AE6" s="3" t="n">
-        <v>11.93881777678433</v>
-      </c>
-      <c r="AF6" s="3" t="n">
-        <v>79.80809096044713</v>
-      </c>
-      <c r="AG6" s="3" t="inlineStr">
+      <c r="Z6" s="2" t="n">
+        <v>141.6377285485467</v>
+      </c>
+      <c r="AA6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="2" t="n">
+        <v>13.00716498201259</v>
+      </c>
+      <c r="AD6" s="2" t="n">
+        <v>80.23866508993706</v>
+      </c>
+      <c r="AE6" s="2" t="n">
+        <v>11.93203161103106</v>
+      </c>
+      <c r="AF6" s="2" t="n">
+        <v>79.80775894691541</v>
+      </c>
+      <c r="AG6" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH6" s="3" t="inlineStr">
+      <c r="AH6" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI6" s="3" t="inlineStr">
+      <c r="AI6" s="2" t="inlineStr">
         <is>
           <t>PAIR_005 | NONSTRICT | Chennai to Pondicherry</t>
         </is>
       </c>
-      <c r="AJ6" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:01</t>
-        </is>
-      </c>
-      <c r="AL6" s="3" t="n">
-        <v>1133</v>
-      </c>
-      <c r="AM6" s="3" t="n">
-        <v>588</v>
-      </c>
-      <c r="AN6" s="3" t="n">
-        <v>11986.808</v>
-      </c>
-      <c r="AO6" s="3" t="n">
-        <v>16362.526</v>
-      </c>
-      <c r="AP6" s="3" t="n">
-        <v>147806.3808897662</v>
-      </c>
-      <c r="AQ6" s="3" t="n">
-        <v>147734.7082243864</v>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:19</t>
+        </is>
+      </c>
+      <c r="AL6" s="2" t="n">
+        <v>1094</v>
+      </c>
+      <c r="AM6" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AN6" s="2" t="n">
+        <v>12575.515</v>
+      </c>
+      <c r="AO6" s="2" t="n">
+        <v>13269</v>
+      </c>
+      <c r="AP6" s="2" t="n">
+        <v>141622.00313376</v>
+      </c>
+      <c r="AQ6" s="2" t="n">
+        <v>141671.1046862772</v>
       </c>
     </row>
     <row r="7">
@@ -1617,17 +1626,17 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>CAND_014</t>
+          <t>CAND_005</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -1652,73 +1661,73 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>15-07-2026</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16-07-2026</t>
+          <t>15-07-2026_to_17-07-2026</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_006_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_17-07-2026\PAIR_006_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>verified_dd675143a782cf2f</t>
+          <t>verified_bc64c4f5f8b414f6</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>verified_17c1217215b4058d</t>
+          <t>verified_241aada409fad48e</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 14:16:16.867715</t>
+          <t>2026-07-17 07:51:32.508934646</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 18:17:39.287281</t>
+          <t>2026-07-17 11:33:03.533645081</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 16:37:54.000000</t>
+          <t>2026-07-15 11:20:23.000000000</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16 20:39:30.945718</t>
+          <t>2026-07-15 15:54:44.000000000</t>
         </is>
       </c>
       <c r="T7" s="2" t="n">
-        <v>143.67832745766</v>
+        <v>148.2084119453301</v>
       </c>
       <c r="U7" s="2" t="n">
-        <v>143.7061031155852</v>
+        <v>148.1502195739105</v>
       </c>
       <c r="V7" s="2" t="n">
-        <v>0.0277756579251331</v>
+        <v>0.0581923714196079</v>
       </c>
       <c r="W7" s="2" t="n">
-        <v>0.0193318355082594</v>
+        <v>0.0392793015001752</v>
       </c>
       <c r="X7" s="2" t="n">
-        <v>2.873566549153201</v>
+        <v>2.96300439147821</v>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
@@ -1726,25 +1735,25 @@
         </is>
       </c>
       <c r="Z7" s="2" t="n">
-        <v>143.6746870919839</v>
+        <v>148.1187897046324</v>
       </c>
       <c r="AA7" s="2" t="n">
+        <v>0.9979108635097492</v>
+      </c>
+      <c r="AB7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB7" s="2" t="n">
-        <v>0.9830910692831158</v>
-      </c>
       <c r="AC7" s="2" t="n">
-        <v>11.94076095220559</v>
+        <v>13.03202304255905</v>
       </c>
       <c r="AD7" s="2" t="n">
-        <v>79.80822915664513</v>
+        <v>80.21127683194683</v>
       </c>
       <c r="AE7" s="2" t="n">
-        <v>13.00921698321911</v>
+        <v>11.938534510264</v>
       </c>
       <c r="AF7" s="2" t="n">
-        <v>80.21242477252731</v>
+        <v>79.80805779812951</v>
       </c>
       <c r="AG7" s="2" t="inlineStr">
         <is>
@@ -1758,579 +1767,579 @@
       </c>
       <c r="AI7" s="2" t="inlineStr">
         <is>
-          <t>PAIR_006 | STRICT | Pondicherry to Chennai</t>
+          <t>PAIR_006 | NONSTRICT | Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="AJ7" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK7" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:05</t>
+          <t>29-09-2026 12:15:19</t>
         </is>
       </c>
       <c r="AL7" s="2" t="n">
-        <v>1102</v>
+        <v>1155</v>
       </c>
       <c r="AM7" s="2" t="n">
-        <v>1089</v>
+        <v>591</v>
       </c>
       <c r="AN7" s="2" t="n">
-        <v>14482.419</v>
+        <v>13291.025</v>
       </c>
       <c r="AO7" s="2" t="n">
-        <v>14496.946</v>
+        <v>16461</v>
       </c>
       <c r="AP7" s="2" t="n">
-        <v>143678.3274576589</v>
+        <v>148208.411945328</v>
       </c>
       <c r="AQ7" s="2" t="n">
-        <v>143706.1031155877</v>
+        <v>148150.219573912</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>PAIR_007</t>
         </is>
       </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>CAND_017</t>
-        </is>
-      </c>
-      <c r="D8" s="3" t="inlineStr">
-        <is>
-          <t>Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>CAND_012</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>PASSED</t>
-        </is>
-      </c>
-      <c r="H8" s="3" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_WITH_SPARSE_TELEMETRY_WARNING</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026</t>
-        </is>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026_to_18-07-2026</t>
-        </is>
-      </c>
-      <c r="L8" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_007_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t>verified_dd675143a782cf2f</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t>verified_ef321ab03753f3e9</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 14:16:16.867715</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 17:07:49.637499</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 16:20:34.000000</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 19:28:38.045576</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="n">
-        <v>126.5032721812737</v>
-      </c>
-      <c r="U8" s="3" t="n">
-        <v>126.4504264596254</v>
-      </c>
-      <c r="V8" s="3" t="n">
-        <v>0.052845721648282</v>
-      </c>
-      <c r="W8" s="3" t="n">
-        <v>0.0417916515806732</v>
-      </c>
-      <c r="X8" s="3" t="n">
-        <v>2.529008529192508</v>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026_to_19-07-2026</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_007_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>verified_99ae97f04e26ba5b</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>verified_1054093294ed2491</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 09:38:15.771280068</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 13:31:09.265001990</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:08:45.000000000</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:37:58.000000000</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="n">
+        <v>146.1103622297153</v>
+      </c>
+      <c r="U8" s="2" t="n">
+        <v>146.1941703909384</v>
+      </c>
+      <c r="V8" s="2" t="n">
+        <v>0.08380816122317469</v>
+      </c>
+      <c r="W8" s="2" t="n">
+        <v>0.0573594917870446</v>
+      </c>
+      <c r="X8" s="2" t="n">
+        <v>2.922207244594305</v>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z8" s="3" t="n">
-        <v>126.44842951288</v>
-      </c>
-      <c r="AA8" s="3" t="n">
+      <c r="Z8" s="2" t="n">
+        <v>146.1331428606738</v>
+      </c>
+      <c r="AA8" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB8" s="3" t="n">
-        <v>0.9172781854569714</v>
-      </c>
-      <c r="AC8" s="3" t="n">
-        <v>11.94078595220559</v>
-      </c>
-      <c r="AD8" s="3" t="n">
-        <v>79.80823415664511</v>
-      </c>
-      <c r="AE8" s="3" t="n">
-        <v>12.89681238111264</v>
-      </c>
-      <c r="AF8" s="3" t="n">
-        <v>80.24722201467677</v>
-      </c>
-      <c r="AG8" s="3" t="inlineStr">
+      <c r="AB8" s="2" t="n">
+        <v>0.9997581089427278</v>
+      </c>
+      <c r="AC8" s="2" t="n">
+        <v>13.00874734835186</v>
+      </c>
+      <c r="AD8" s="2" t="n">
+        <v>80.21068754867539</v>
+      </c>
+      <c r="AE8" s="2" t="n">
+        <v>11.93232918472765</v>
+      </c>
+      <c r="AF8" s="2" t="n">
+        <v>79.81457511188292</v>
+      </c>
+      <c r="AG8" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH8" s="3" t="inlineStr">
+      <c r="AH8" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI8" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_007 | NONSTRICT | Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="AJ8" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK8" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:09</t>
-        </is>
-      </c>
-      <c r="AL8" s="3" t="n">
-        <v>960</v>
-      </c>
-      <c r="AM8" s="3" t="n">
-        <v>988</v>
-      </c>
-      <c r="AN8" s="3" t="n">
-        <v>10292.769</v>
-      </c>
-      <c r="AO8" s="3" t="n">
-        <v>11284.046</v>
-      </c>
-      <c r="AP8" s="3" t="n">
-        <v>126503.272181271</v>
-      </c>
-      <c r="AQ8" s="3" t="n">
-        <v>126450.4264596244</v>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_007 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:20</t>
+        </is>
+      </c>
+      <c r="AL8" s="2" t="n">
+        <v>1160</v>
+      </c>
+      <c r="AM8" s="2" t="n">
+        <v>1116</v>
+      </c>
+      <c r="AN8" s="2" t="n">
+        <v>13973.494</v>
+      </c>
+      <c r="AO8" s="2" t="n">
+        <v>16153</v>
+      </c>
+      <c r="AP8" s="2" t="n">
+        <v>146110.3622297162</v>
+      </c>
+      <c r="AQ8" s="2" t="n">
+        <v>146194.1703909393</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>PAIR_008</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C9" s="3" t="inlineStr">
-        <is>
-          <t>CAND_018</t>
-        </is>
-      </c>
-      <c r="D9" s="3" t="inlineStr">
-        <is>
-          <t>Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>COMMON_ROUTE_SEGMENT_TAT</t>
-        </is>
-      </c>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>CAND_007</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I9" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026_to_18-07-2026</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="M9" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_008_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="N9" s="3" t="inlineStr">
-        <is>
-          <t>verified_e7fad6dcd15297c9</t>
-        </is>
-      </c>
-      <c r="O9" s="3" t="inlineStr">
-        <is>
-          <t>verified_17c1217215b4058d</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 14:14:38.786008</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 17:18:32.519256</t>
-        </is>
-      </c>
-      <c r="R9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 16:37:54.000000</t>
-        </is>
-      </c>
-      <c r="S9" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 19:38:12.334908</t>
-        </is>
-      </c>
-      <c r="T9" s="3" t="n">
-        <v>126.6046070482777</v>
-      </c>
-      <c r="U9" s="3" t="n">
-        <v>126.5641866441437</v>
-      </c>
-      <c r="V9" s="3" t="n">
-        <v>0.0404204041340392</v>
-      </c>
-      <c r="W9" s="3" t="n">
-        <v>0.0319366838327559</v>
-      </c>
-      <c r="X9" s="3" t="n">
-        <v>2.531283732882874</v>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026_to_19-07-2026</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_19-07-2026\PAIR_008_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>verified_15412510a4af5bed</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>verified_241aada409fad48e</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:10:36.000000000</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:30:22.807910573</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:22:01.474402369</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:54:44.000000000</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="n">
+        <v>147.8063808897641</v>
+      </c>
+      <c r="U9" s="2" t="n">
+        <v>147.7347082243845</v>
+      </c>
+      <c r="V9" s="2" t="n">
+        <v>0.07167266537959439</v>
+      </c>
+      <c r="W9" s="2" t="n">
+        <v>0.0485144393223667</v>
+      </c>
+      <c r="X9" s="2" t="n">
+        <v>2.954694164487689</v>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z9" s="3" t="n">
-        <v>126.5492479870981</v>
-      </c>
-      <c r="AA9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="3" t="n">
-        <v>0.865910607071381</v>
-      </c>
-      <c r="AC9" s="3" t="n">
-        <v>11.94059495370101</v>
-      </c>
-      <c r="AD9" s="3" t="n">
-        <v>79.80821544753046</v>
-      </c>
-      <c r="AE9" s="3" t="n">
-        <v>12.89757340115048</v>
-      </c>
-      <c r="AF9" s="3" t="n">
-        <v>80.24729370987414</v>
-      </c>
-      <c r="AG9" s="3" t="inlineStr">
+      <c r="Z9" s="2" t="n">
+        <v>147.7235427674619</v>
+      </c>
+      <c r="AA9" s="2" t="n">
+        <v>0.9993270524899058</v>
+      </c>
+      <c r="AB9" s="2" t="n">
+        <v>0.9973315543695797</v>
+      </c>
+      <c r="AC9" s="2" t="n">
+        <v>13.03021900769515</v>
+      </c>
+      <c r="AD9" s="2" t="n">
+        <v>80.20912883276921</v>
+      </c>
+      <c r="AE9" s="2" t="n">
+        <v>11.93881777678433</v>
+      </c>
+      <c r="AF9" s="2" t="n">
+        <v>79.80809096044713</v>
+      </c>
+      <c r="AG9" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH9" s="3" t="inlineStr">
+      <c r="AH9" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI9" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_008 | NONSTRICT | Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="AJ9" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:12</t>
-        </is>
-      </c>
-      <c r="AL9" s="3" t="n">
-        <v>978</v>
-      </c>
-      <c r="AM9" s="3" t="n">
-        <v>949</v>
-      </c>
-      <c r="AN9" s="3" t="n">
-        <v>11033.733</v>
-      </c>
-      <c r="AO9" s="3" t="n">
-        <v>10818.335</v>
-      </c>
-      <c r="AP9" s="3" t="n">
-        <v>126604.6070482763</v>
-      </c>
-      <c r="AQ9" s="3" t="n">
-        <v>126564.1866441461</v>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_008 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:20</t>
+        </is>
+      </c>
+      <c r="AL9" s="2" t="n">
+        <v>1133</v>
+      </c>
+      <c r="AM9" s="2" t="n">
+        <v>588</v>
+      </c>
+      <c r="AN9" s="2" t="n">
+        <v>11986.808</v>
+      </c>
+      <c r="AO9" s="2" t="n">
+        <v>16362.526</v>
+      </c>
+      <c r="AP9" s="2" t="n">
+        <v>147806.3808897662</v>
+      </c>
+      <c r="AQ9" s="2" t="n">
+        <v>147734.7082243864</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>PAIR_009</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>CAND_019</t>
-        </is>
-      </c>
-      <c r="D10" s="3" t="inlineStr">
-        <is>
-          <t>Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>COMMON_ROUTE_SEGMENT_TAT</t>
-        </is>
-      </c>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>CAND_010</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H10" s="3" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I10" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026</t>
-        </is>
-      </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>16-07-2026_to_20-07-2026</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="M10" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_009_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="N10" s="3" t="inlineStr">
-        <is>
-          <t>verified_dd675143a782cf2f</t>
-        </is>
-      </c>
-      <c r="O10" s="3" t="inlineStr">
-        <is>
-          <t>verified_b6771ff18a5dc98d</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 14:52:08.455942</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-16 18:17:53.688637</t>
-        </is>
-      </c>
-      <c r="R10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:56:44.000000</t>
-        </is>
-      </c>
-      <c r="S10" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 20:11:41.503875</t>
-        </is>
-      </c>
-      <c r="T10" s="3" t="n">
-        <v>123.9185956857722</v>
-      </c>
-      <c r="U10" s="3" t="n">
-        <v>123.9419360729098</v>
-      </c>
-      <c r="V10" s="3" t="n">
-        <v>0.0233403871375372</v>
-      </c>
-      <c r="W10" s="3" t="n">
-        <v>0.0188352579436284</v>
-      </c>
-      <c r="X10" s="3" t="n">
-        <v>2.478371913715444</v>
-      </c>
-      <c r="Y10" s="3" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>15-07-2026_to_25-09-2026</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\15-07-2026_to_25-09-2026\PAIR_009_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>verified_857b5a523fbbfc53</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>verified_241aada409fad48e</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:45:53.056570634</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:53:09.116041191</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 11:20:23.000000000</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-15 15:54:44.000000000</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="n">
+        <v>148.4551342034193</v>
+      </c>
+      <c r="U10" s="2" t="n">
+        <v>148.169342051972</v>
+      </c>
+      <c r="V10" s="2" t="n">
+        <v>0.2857921514472821</v>
+      </c>
+      <c r="W10" s="2" t="n">
+        <v>0.1928821087340979</v>
+      </c>
+      <c r="X10" s="2" t="n">
+        <v>2.96338684103944</v>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z10" s="3" t="n">
-        <v>123.9181246480898</v>
-      </c>
-      <c r="AA10" s="3" t="n">
-        <v>0.9986366734832992</v>
-      </c>
-      <c r="AB10" s="3" t="n">
-        <v>0.9778536071038711</v>
-      </c>
-      <c r="AC10" s="3" t="n">
-        <v>12.09244084320738</v>
-      </c>
-      <c r="AD10" s="3" t="n">
-        <v>79.89408241392127</v>
-      </c>
-      <c r="AE10" s="3" t="n">
-        <v>13.00894694718269</v>
-      </c>
-      <c r="AF10" s="3" t="n">
-        <v>80.2117661649247</v>
-      </c>
-      <c r="AG10" s="3" t="inlineStr">
+      <c r="Z10" s="2" t="n">
+        <v>148.1187897046324</v>
+      </c>
+      <c r="AA10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="2" t="n">
+        <v>13.031925</v>
+      </c>
+      <c r="AD10" s="2" t="n">
+        <v>80.21136386858731</v>
+      </c>
+      <c r="AE10" s="2" t="n">
+        <v>11.93845919794042</v>
+      </c>
+      <c r="AF10" s="2" t="n">
+        <v>79.80803176791761</v>
+      </c>
+      <c r="AG10" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH10" s="3" t="inlineStr">
+      <c r="AH10" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI10" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_009 | NONSTRICT | Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="AJ10" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:16</t>
-        </is>
-      </c>
-      <c r="AL10" s="3" t="n">
-        <v>964</v>
-      </c>
-      <c r="AM10" s="3" t="n">
-        <v>950</v>
-      </c>
-      <c r="AN10" s="3" t="n">
-        <v>12345.233</v>
-      </c>
-      <c r="AO10" s="3" t="n">
-        <v>11697.504</v>
-      </c>
-      <c r="AP10" s="3" t="n">
-        <v>123918.5956857711</v>
-      </c>
-      <c r="AQ10" s="3" t="n">
-        <v>123941.936072907</v>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_009 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:21</t>
+        </is>
+      </c>
+      <c r="AL10" s="2" t="n">
+        <v>2306</v>
+      </c>
+      <c r="AM10" s="2" t="n">
+        <v>591</v>
+      </c>
+      <c r="AN10" s="2" t="n">
+        <v>14836.059</v>
+      </c>
+      <c r="AO10" s="2" t="n">
+        <v>16461</v>
+      </c>
+      <c r="AP10" s="2" t="n">
+        <v>148455.1342034233</v>
+      </c>
+      <c r="AQ10" s="2" t="n">
+        <v>148169.3420519741</v>
       </c>
     </row>
     <row r="11">
@@ -2341,12 +2350,12 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>CAND_020</t>
+          <t>CAND_023</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
@@ -2376,7 +2385,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -2386,63 +2395,63 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>16-07-2026_to_20-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_010_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026\PAIR_010_STRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>verified_2e8f3bf6137add72</t>
+          <t>verified_95fc6af6c7b70a5b</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>verified_17c1217215b4058d</t>
+          <t>verified_449311acdf960595</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20 14:14:55.177888</t>
+          <t>2026-07-16 14:16:16.867715598</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20 17:57:57.696631</t>
+          <t>2026-07-16 18:17:39.287281516</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 16:37:54.000000</t>
+          <t>2026-07-16 16:37:54.000000000</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t>2026-07-16 20:39:30.945718</t>
+          <t>2026-07-16 20:39:30.945718227</t>
         </is>
       </c>
       <c r="T11" s="3" t="n">
-        <v>143.7155596131444</v>
+        <v>143.67832745766</v>
       </c>
       <c r="U11" s="3" t="n">
-        <v>143.7030109884497</v>
+        <v>143.7061031155852</v>
       </c>
       <c r="V11" s="3" t="n">
-        <v>0.0125486246947161</v>
+        <v>0.0277756579251331</v>
       </c>
       <c r="W11" s="3" t="n">
-        <v>0.008732332474038901</v>
+        <v>0.0193318355082594</v>
       </c>
       <c r="X11" s="3" t="n">
-        <v>2.874060219768994</v>
+        <v>2.873566549153201</v>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
@@ -2450,25 +2459,25 @@
         </is>
       </c>
       <c r="Z11" s="3" t="n">
-        <v>143.7084680531453</v>
+        <v>143.6746870919839</v>
       </c>
       <c r="AA11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AB11" s="3" t="n">
-        <v>0.9833222148098734</v>
+        <v>0.9830910692831158</v>
       </c>
       <c r="AC11" s="3" t="n">
-        <v>11.94077473611527</v>
+        <v>11.94076095220559</v>
       </c>
       <c r="AD11" s="3" t="n">
-        <v>79.80824975984353</v>
+        <v>79.80822915664513</v>
       </c>
       <c r="AE11" s="3" t="n">
-        <v>13.00917955032714</v>
+        <v>13.00921698321911</v>
       </c>
       <c r="AF11" s="3" t="n">
-        <v>80.21245072524952</v>
+        <v>80.21242477252731</v>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
@@ -2482,36 +2491,36 @@
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>PAIR_010 | NONSTRICT | Pondicherry to Chennai</t>
+          <t>PAIR_010 | STRICT | Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK11" s="3" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:22</t>
+          <t>29-09-2026 12:15:22</t>
         </is>
       </c>
       <c r="AL11" s="3" t="n">
-        <v>1145</v>
+        <v>1102</v>
       </c>
       <c r="AM11" s="3" t="n">
         <v>1089</v>
       </c>
       <c r="AN11" s="3" t="n">
-        <v>13382.519</v>
+        <v>14482.419</v>
       </c>
       <c r="AO11" s="3" t="n">
         <v>14496.946</v>
       </c>
       <c r="AP11" s="3" t="n">
-        <v>143715.559613142</v>
+        <v>143678.3274576589</v>
       </c>
       <c r="AQ11" s="3" t="n">
-        <v>143703.0109884508</v>
+        <v>143706.1031155877</v>
       </c>
     </row>
     <row r="12">
@@ -2522,22 +2531,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>CAND_002</t>
+          <t>CAND_026</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Chennai to Pondicherry</t>
+          <t>Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -2557,73 +2566,73 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>18-07-2026</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17-07-2026</t>
+          <t>16-07-2026_to_18-07-2026</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_011_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_011_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>verified_7c397965c0f14f48</t>
+          <t>verified_95fc6af6c7b70a5b</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>verified_af2997304a2169c1</t>
+          <t>verified_5a4bc25af139b115</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17 08:09:07.711647</t>
+          <t>2026-07-16 14:16:16.867715598</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17 11:34:46.317203</t>
+          <t>2026-07-16 17:07:49.637499389</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17 11:43:51.000000</t>
+          <t>2026-07-18 16:20:34.000000000</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2026-07-17 15:25:00.000000</t>
+          <t>2026-07-18 19:28:38.045576935</t>
         </is>
       </c>
       <c r="T12" s="2" t="n">
-        <v>141.5990549680245</v>
+        <v>126.5032721812737</v>
       </c>
       <c r="U12" s="2" t="n">
-        <v>141.6663057069567</v>
+        <v>126.4504264596254</v>
       </c>
       <c r="V12" s="2" t="n">
-        <v>0.0672507389321879</v>
+        <v>0.052845721648282</v>
       </c>
       <c r="W12" s="2" t="n">
-        <v>0.0474937766691834</v>
+        <v>0.0417916515806732</v>
       </c>
       <c r="X12" s="2" t="n">
-        <v>2.831981099360491</v>
+        <v>2.529008529192508</v>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
@@ -2631,25 +2640,25 @@
         </is>
       </c>
       <c r="Z12" s="2" t="n">
-        <v>141.6305635069461</v>
+        <v>126.44842951288</v>
       </c>
       <c r="AA12" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB12" s="2" t="n">
-        <v>0.999949412902381</v>
+        <v>0.9172781854569714</v>
       </c>
       <c r="AC12" s="2" t="n">
-        <v>13.00715678741182</v>
+        <v>11.94078595220559</v>
       </c>
       <c r="AD12" s="2" t="n">
-        <v>80.23868250470565</v>
+        <v>79.80823415664511</v>
       </c>
       <c r="AE12" s="2" t="n">
-        <v>11.93207336276102</v>
+        <v>12.89681238111264</v>
       </c>
       <c r="AF12" s="2" t="n">
-        <v>79.80784084422952</v>
+        <v>80.24722201467677</v>
       </c>
       <c r="AG12" s="2" t="inlineStr">
         <is>
@@ -2663,398 +2672,398 @@
       </c>
       <c r="AI12" s="2" t="inlineStr">
         <is>
-          <t>PAIR_011 | STRICT | Chennai to Pondicherry</t>
+          <t>PAIR_011 | NONSTRICT | Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="AJ12" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK12" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:29</t>
+          <t>29-09-2026 12:15:22</t>
         </is>
       </c>
       <c r="AL12" s="2" t="n">
-        <v>1101</v>
+        <v>960</v>
       </c>
       <c r="AM12" s="2" t="n">
-        <v>1024</v>
+        <v>988</v>
       </c>
       <c r="AN12" s="2" t="n">
-        <v>12338.605</v>
+        <v>10292.769</v>
       </c>
       <c r="AO12" s="2" t="n">
-        <v>13269</v>
+        <v>11284.046</v>
       </c>
       <c r="AP12" s="2" t="n">
-        <v>141599.0549680233</v>
+        <v>126503.272181271</v>
       </c>
       <c r="AQ12" s="2" t="n">
-        <v>141666.3057069586</v>
+        <v>126450.4264596244</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>PAIR_012</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>CAND_005</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>CAND_027</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H13" s="3" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>19-07-2026</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026_to_19-07-2026</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_012_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>verified_7c397965c0f14f48</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>verified_49abd2a79268e808</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 07:59:53.804941</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 11:39:50.000000</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 11:08:45.000000</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 15:37:58.000000</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="n">
-        <v>146.1177802267275</v>
-      </c>
-      <c r="U13" s="3" t="n">
-        <v>146.2265476173814</v>
-      </c>
-      <c r="V13" s="3" t="n">
-        <v>0.1087673906538384</v>
-      </c>
-      <c r="W13" s="3" t="n">
-        <v>0.074438162477603</v>
-      </c>
-      <c r="X13" s="3" t="n">
-        <v>2.922355604534551</v>
-      </c>
-      <c r="Y13" s="3" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026_to_18-07-2026</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_18-07-2026\PAIR_012_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>verified_09767f5cfc6bbb35</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>verified_449311acdf960595</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:14:38.786008121</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:18:32.519256376</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:37:54.000000000</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 19:38:12.334908498</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="n">
+        <v>126.6046070482777</v>
+      </c>
+      <c r="U13" s="2" t="n">
+        <v>126.5641866441437</v>
+      </c>
+      <c r="V13" s="2" t="n">
+        <v>0.0404204041340392</v>
+      </c>
+      <c r="W13" s="2" t="n">
+        <v>0.0319366838327559</v>
+      </c>
+      <c r="X13" s="2" t="n">
+        <v>2.531283732882874</v>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z13" s="3" t="n">
-        <v>146.1684997136095</v>
-      </c>
-      <c r="AA13" s="3" t="n">
+      <c r="Z13" s="2" t="n">
+        <v>126.5492479870981</v>
+      </c>
+      <c r="AA13" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB13" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="3" t="n">
-        <v>13.00872658647151</v>
-      </c>
-      <c r="AD13" s="3" t="n">
-        <v>80.21065041741409</v>
-      </c>
-      <c r="AE13" s="3" t="n">
-        <v>11.93232</v>
-      </c>
-      <c r="AF13" s="3" t="n">
-        <v>79.81483499999999</v>
-      </c>
-      <c r="AG13" s="3" t="inlineStr">
+      <c r="AB13" s="2" t="n">
+        <v>0.865910607071381</v>
+      </c>
+      <c r="AC13" s="2" t="n">
+        <v>11.94059495370101</v>
+      </c>
+      <c r="AD13" s="2" t="n">
+        <v>79.80821544753046</v>
+      </c>
+      <c r="AE13" s="2" t="n">
+        <v>12.89757340115048</v>
+      </c>
+      <c r="AF13" s="2" t="n">
+        <v>80.24729370987414</v>
+      </c>
+      <c r="AG13" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH13" s="3" t="inlineStr">
+      <c r="AH13" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI13" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_012 | NONSTRICT | Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="AJ13" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK13" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:36</t>
-        </is>
-      </c>
-      <c r="AL13" s="3" t="n">
-        <v>1142</v>
-      </c>
-      <c r="AM13" s="3" t="n">
-        <v>1116</v>
-      </c>
-      <c r="AN13" s="3" t="n">
-        <v>13196.195</v>
-      </c>
-      <c r="AO13" s="3" t="n">
-        <v>16153</v>
-      </c>
-      <c r="AP13" s="3" t="n">
-        <v>146117.7802267258</v>
-      </c>
-      <c r="AQ13" s="3" t="n">
-        <v>146226.5476173816</v>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_012 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:23</t>
+        </is>
+      </c>
+      <c r="AL13" s="2" t="n">
+        <v>978</v>
+      </c>
+      <c r="AM13" s="2" t="n">
+        <v>949</v>
+      </c>
+      <c r="AN13" s="2" t="n">
+        <v>11033.733</v>
+      </c>
+      <c r="AO13" s="2" t="n">
+        <v>10818.335</v>
+      </c>
+      <c r="AP13" s="2" t="n">
+        <v>126604.6070482763</v>
+      </c>
+      <c r="AQ13" s="2" t="n">
+        <v>126564.1866441461</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>PAIR_013</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C14" s="3" t="inlineStr">
-        <is>
-          <t>CAND_003</t>
-        </is>
-      </c>
-      <c r="D14" s="3" t="inlineStr">
-        <is>
-          <t>Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="F14" s="3" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>CAND_028</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H14" s="3" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>19-07-2026</t>
-        </is>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t>17-07-2026_to_19-07-2026</t>
-        </is>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_013_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t>verified_bdff61acc7fcadf8</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t>verified_af2997304a2169c1</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 09:26:56.323520</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-19 12:33:03.257434</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 11:43:51.000000</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-17 15:25:00.000000</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="n">
-        <v>141.7178099447914</v>
-      </c>
-      <c r="U14" s="3" t="n">
-        <v>141.7137294264354</v>
-      </c>
-      <c r="V14" s="3" t="n">
-        <v>0.0040805183560621</v>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v>0.0028794093363977</v>
-      </c>
-      <c r="X14" s="3" t="n">
-        <v>2.834274588528708</v>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026_to_20-07-2026</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_013_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>verified_95fc6af6c7b70a5b</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>verified_f4d3e9223e856e32</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 14:52:08.455942257</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 18:17:53.688637879</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:56:44.000000000</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 20:11:41.503875467</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="n">
+        <v>123.9185956857722</v>
+      </c>
+      <c r="U14" s="2" t="n">
+        <v>123.9419360729098</v>
+      </c>
+      <c r="V14" s="2" t="n">
+        <v>0.0233403871375372</v>
+      </c>
+      <c r="W14" s="2" t="n">
+        <v>0.0188352579436284</v>
+      </c>
+      <c r="X14" s="2" t="n">
+        <v>2.478371913715444</v>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v>141.6377285485467</v>
-      </c>
-      <c r="AA14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="3" t="n">
-        <v>13.00724677951333</v>
-      </c>
-      <c r="AD14" s="3" t="n">
-        <v>80.23829613187164</v>
-      </c>
-      <c r="AE14" s="3" t="n">
-        <v>11.93202161710183</v>
-      </c>
-      <c r="AF14" s="3" t="n">
-        <v>79.80778733363579</v>
-      </c>
-      <c r="AG14" s="3" t="inlineStr">
+      <c r="Z14" s="2" t="n">
+        <v>123.9181246480898</v>
+      </c>
+      <c r="AA14" s="2" t="n">
+        <v>0.9986366734832992</v>
+      </c>
+      <c r="AB14" s="2" t="n">
+        <v>0.9778536071038711</v>
+      </c>
+      <c r="AC14" s="2" t="n">
+        <v>12.09244084320738</v>
+      </c>
+      <c r="AD14" s="2" t="n">
+        <v>79.89408241392127</v>
+      </c>
+      <c r="AE14" s="2" t="n">
+        <v>13.00894694718269</v>
+      </c>
+      <c r="AF14" s="2" t="n">
+        <v>80.2117661649247</v>
+      </c>
+      <c r="AG14" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH14" s="3" t="inlineStr">
+      <c r="AH14" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI14" s="3" t="inlineStr">
-        <is>
-          <t>PAIR_013 | NONSTRICT | Chennai to Pondicherry</t>
-        </is>
-      </c>
-      <c r="AJ14" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:43</t>
-        </is>
-      </c>
-      <c r="AL14" s="3" t="n">
-        <v>1073</v>
-      </c>
-      <c r="AM14" s="3" t="n">
-        <v>1024</v>
-      </c>
-      <c r="AN14" s="3" t="n">
-        <v>11166.933</v>
-      </c>
-      <c r="AO14" s="3" t="n">
-        <v>13269</v>
-      </c>
-      <c r="AP14" s="3" t="n">
-        <v>141717.8099447946</v>
-      </c>
-      <c r="AQ14" s="3" t="n">
-        <v>141713.7294264383</v>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_013 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:23</t>
+        </is>
+      </c>
+      <c r="AL14" s="2" t="n">
+        <v>964</v>
+      </c>
+      <c r="AM14" s="2" t="n">
+        <v>950</v>
+      </c>
+      <c r="AN14" s="2" t="n">
+        <v>12345.233</v>
+      </c>
+      <c r="AO14" s="2" t="n">
+        <v>11697.504</v>
+      </c>
+      <c r="AP14" s="2" t="n">
+        <v>123918.5956857711</v>
+      </c>
+      <c r="AQ14" s="2" t="n">
+        <v>123941.936072907</v>
       </c>
     </row>
     <row r="15">
@@ -3065,12 +3074,12 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CAND_013</t>
+          <t>CAND_029</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3080,7 +3089,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3100,73 +3109,73 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>20-07-2026</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>16-07-2026</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>16-07-2026_to_20-07-2026</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_014_STRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_20-07-2026\PAIR_014_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>verified_e7fad6dcd15297c9</t>
+          <t>verified_fdd276bba7af4ffb</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>verified_ef321ab03753f3e9</t>
+          <t>verified_449311acdf960595</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18 14:14:38.786008</t>
+          <t>2026-07-20 14:14:55.177888204</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18 17:19:31.142914</t>
+          <t>2026-07-20 17:57:57.696631389</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18 16:20:34.000000</t>
+          <t>2026-07-16 16:37:54.000000000</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2026-07-18 19:30:23.423595</t>
+          <t>2026-07-16 20:39:30.945718227</t>
         </is>
       </c>
       <c r="T15" s="2" t="n">
-        <v>126.7971112808863</v>
+        <v>143.7155596131444</v>
       </c>
       <c r="U15" s="2" t="n">
-        <v>126.7676219192401</v>
+        <v>143.7030109884497</v>
       </c>
       <c r="V15" s="2" t="n">
-        <v>0.0294893616461848</v>
+        <v>0.0125486246947161</v>
       </c>
       <c r="W15" s="2" t="n">
-        <v>0.0232625343914486</v>
+        <v>0.008732332474038901</v>
       </c>
       <c r="X15" s="2" t="n">
-        <v>2.535352438384801</v>
+        <v>2.874060219768994</v>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
@@ -3174,25 +3183,25 @@
         </is>
       </c>
       <c r="Z15" s="2" t="n">
-        <v>126.7243169954536</v>
+        <v>143.7084680531453</v>
       </c>
       <c r="AA15" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB15" s="2" t="n">
-        <v>0.9192795196797864</v>
+        <v>0.9833222148098734</v>
       </c>
       <c r="AC15" s="2" t="n">
-        <v>11.94061995370101</v>
+        <v>11.94077473611527</v>
       </c>
       <c r="AD15" s="2" t="n">
-        <v>79.80822044753046</v>
+        <v>79.80824975984353</v>
       </c>
       <c r="AE15" s="2" t="n">
-        <v>12.89809640493977</v>
+        <v>13.00917955032714</v>
       </c>
       <c r="AF15" s="2" t="n">
-        <v>80.24542875618252</v>
+        <v>80.21245072524952</v>
       </c>
       <c r="AG15" s="2" t="inlineStr">
         <is>
@@ -3206,217 +3215,217 @@
       </c>
       <c r="AI15" s="2" t="inlineStr">
         <is>
-          <t>PAIR_014 | STRICT | Pondicherry to Chennai</t>
+          <t>PAIR_014 | NONSTRICT | Pondicherry to Chennai</t>
         </is>
       </c>
       <c r="AJ15" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK15" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:46</t>
+          <t>29-09-2026 12:15:24</t>
         </is>
       </c>
       <c r="AL15" s="2" t="n">
-        <v>979</v>
+        <v>1145</v>
       </c>
       <c r="AM15" s="2" t="n">
-        <v>992</v>
+        <v>1089</v>
       </c>
       <c r="AN15" s="2" t="n">
-        <v>11092.357</v>
+        <v>13382.519</v>
       </c>
       <c r="AO15" s="2" t="n">
-        <v>11389.424</v>
+        <v>14496.946</v>
       </c>
       <c r="AP15" s="2" t="n">
-        <v>126797.111280885</v>
+        <v>143715.559613142</v>
       </c>
       <c r="AQ15" s="2" t="n">
-        <v>126767.6219192398</v>
+        <v>143703.0109884508</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>PAIR_015</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NONSTRICT</t>
         </is>
       </c>
-      <c r="C16" s="3" t="inlineStr">
-        <is>
-          <t>CAND_016</t>
-        </is>
-      </c>
-      <c r="D16" s="3" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>CAND_032</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Pondicherry to Chennai</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
-      <c r="F16" s="3" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H16" s="3" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I16" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2026</t>
-        </is>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>20-07-2026</t>
-        </is>
-      </c>
-      <c r="K16" s="3" t="inlineStr">
-        <is>
-          <t>18-07-2026_to_20-07-2026</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>16-07-2026_to_26-09-2026</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
         </is>
       </c>
-      <c r="M16" s="3" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="N16" s="3" t="inlineStr">
-        <is>
-          <t>verified_e7fad6dcd15297c9</t>
-        </is>
-      </c>
-      <c r="O16" s="3" t="inlineStr">
-        <is>
-          <t>verified_b6771ff18a5dc98d</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 14:59:13.286758</t>
-        </is>
-      </c>
-      <c r="Q16" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-18 17:18:32.519256</t>
-        </is>
-      </c>
-      <c r="R16" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:56:44.000000</t>
-        </is>
-      </c>
-      <c r="S16" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20 19:26:14.650937</t>
-        </is>
-      </c>
-      <c r="T16" s="3" t="n">
-        <v>106.7510397234517</v>
-      </c>
-      <c r="U16" s="3" t="n">
-        <v>106.7303536725832</v>
-      </c>
-      <c r="V16" s="3" t="n">
-        <v>0.0206860508684911</v>
-      </c>
-      <c r="W16" s="3" t="n">
-        <v>0.0193816006006593</v>
-      </c>
-      <c r="X16" s="3" t="n">
-        <v>2.134607073451664</v>
-      </c>
-      <c r="Y16" s="3" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\16-07-2026_to_26-09-2026\PAIR_015_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>verified_2ef63d7709cb5e84</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>verified_449311acdf960595</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:31:24.552784178</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:43:26.486809471</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 16:37:54.000000000</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-16 17:56:14.644528287</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="n">
+        <v>44.16496961682888</v>
+      </c>
+      <c r="U16" s="2" t="n">
+        <v>44.09816148210977</v>
+      </c>
+      <c r="V16" s="2" t="n">
+        <v>0.06680813471910339</v>
+      </c>
+      <c r="W16" s="2" t="n">
+        <v>0.1514986849195671</v>
+      </c>
+      <c r="X16" s="2" t="n">
+        <v>0.8819632296421955</v>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z16" s="3" t="n">
-        <v>106.6887709766038</v>
-      </c>
-      <c r="AA16" s="3" t="n">
+      <c r="Z16" s="2" t="n">
+        <v>44.06799698780303</v>
+      </c>
+      <c r="AA16" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="AB16" s="3" t="n">
-        <v>0.8418945963975984</v>
-      </c>
-      <c r="AC16" s="3" t="n">
-        <v>12.09212293338802</v>
-      </c>
-      <c r="AD16" s="3" t="n">
-        <v>79.89393395207165</v>
-      </c>
-      <c r="AE16" s="3" t="n">
-        <v>12.89737507024662</v>
-      </c>
-      <c r="AF16" s="3" t="n">
-        <v>80.24725579534282</v>
-      </c>
-      <c r="AG16" s="3" t="inlineStr">
+      <c r="AB16" s="2" t="n">
+        <v>0.3015343562374916</v>
+      </c>
+      <c r="AC16" s="2" t="n">
+        <v>11.94080987528801</v>
+      </c>
+      <c r="AD16" s="2" t="n">
+        <v>79.80825276392089</v>
+      </c>
+      <c r="AE16" s="2" t="n">
+        <v>12.27741664496463</v>
+      </c>
+      <c r="AF16" s="2" t="n">
+        <v>79.98365623040327</v>
+      </c>
+      <c r="AG16" s="2" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH16" s="3" t="inlineStr">
+      <c r="AH16" s="2" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI16" s="3" t="inlineStr">
+      <c r="AI16" s="2" t="inlineStr">
         <is>
           <t>PAIR_015 | NONSTRICT | Pondicherry to Chennai</t>
         </is>
       </c>
-      <c r="AJ16" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:48</t>
-        </is>
-      </c>
-      <c r="AL16" s="3" t="n">
-        <v>830</v>
-      </c>
-      <c r="AM16" s="3" t="n">
-        <v>804</v>
-      </c>
-      <c r="AN16" s="3" t="n">
-        <v>8359.232</v>
-      </c>
-      <c r="AO16" s="3" t="n">
-        <v>8970.651</v>
-      </c>
-      <c r="AP16" s="3" t="n">
-        <v>106751.0397234517</v>
-      </c>
-      <c r="AQ16" s="3" t="n">
-        <v>106730.3536725813</v>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:24</t>
+        </is>
+      </c>
+      <c r="AL16" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="AM16" s="2" t="n">
+        <v>322</v>
+      </c>
+      <c r="AN16" s="2" t="n">
+        <v>4321.934</v>
+      </c>
+      <c r="AO16" s="2" t="n">
+        <v>4700.645</v>
+      </c>
+      <c r="AP16" s="2" t="n">
+        <v>44164.96961682833</v>
+      </c>
+      <c r="AQ16" s="2" t="n">
+        <v>44098.16148211158</v>
       </c>
     </row>
     <row r="17">
@@ -3427,22 +3436,22 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>NONSTRICT</t>
+          <t>STRICT</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>CAND_015</t>
+          <t>CAND_002</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>Pondicherry to Chennai</t>
+          <t>Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -3462,73 +3471,73 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>20-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>18-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>18-07-2026_to_20-07-2026</t>
+          <t>17-07-2026</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_016_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026\PAIR_016_STRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>verified_2e8f3bf6137add72</t>
+          <t>verified_bc64c4f5f8b414f6</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>verified_ef321ab03753f3e9</t>
+          <t>verified_1ce33d8c8868f78e</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20 14:14:55.177888</t>
+          <t>2026-07-17 08:09:07.711647053</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-20 17:01:15.891391</t>
+          <t>2026-07-17 11:34:46.317203786</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 16:20:34.000000</t>
+          <t>2026-07-17 11:43:51.000000000</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t>2026-07-18 19:28:38.045576</t>
+          <t>2026-07-17 15:25:00.000000000</t>
         </is>
       </c>
       <c r="T17" s="3" t="n">
-        <v>126.5111630773056</v>
+        <v>141.5990549680245</v>
       </c>
       <c r="U17" s="3" t="n">
-        <v>126.460973201046</v>
+        <v>141.6663057069567</v>
       </c>
       <c r="V17" s="3" t="n">
-        <v>0.0501898762595942</v>
+        <v>0.0672507389321879</v>
       </c>
       <c r="W17" s="3" t="n">
-        <v>0.0396880357545588</v>
+        <v>0.0474937766691834</v>
       </c>
       <c r="X17" s="3" t="n">
-        <v>2.52921946402092</v>
+        <v>2.831981099360491</v>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
@@ -3536,25 +3545,25 @@
         </is>
       </c>
       <c r="Z17" s="3" t="n">
-        <v>126.44842951288</v>
+        <v>141.6305635069461</v>
       </c>
       <c r="AA17" s="3" t="n">
         <v>1</v>
       </c>
       <c r="AB17" s="3" t="n">
-        <v>0.9172781854569714</v>
+        <v>0.999949412902381</v>
       </c>
       <c r="AC17" s="3" t="n">
-        <v>11.94079973611527</v>
+        <v>13.00715678741182</v>
       </c>
       <c r="AD17" s="3" t="n">
-        <v>79.80825475984354</v>
+        <v>80.23868250470565</v>
       </c>
       <c r="AE17" s="3" t="n">
-        <v>12.89692247679694</v>
+        <v>11.93207336276102</v>
       </c>
       <c r="AF17" s="3" t="n">
-        <v>80.24722803800822</v>
+        <v>79.80784084422952</v>
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
@@ -3568,36 +3577,36 @@
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>PAIR_016 | NONSTRICT | Pondicherry to Chennai</t>
+          <t>PAIR_016 | STRICT | Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK17" s="3" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:51</t>
+          <t>29-09-2026 12:15:25</t>
         </is>
       </c>
       <c r="AL17" s="3" t="n">
-        <v>983</v>
+        <v>1101</v>
       </c>
       <c r="AM17" s="3" t="n">
-        <v>988</v>
+        <v>1024</v>
       </c>
       <c r="AN17" s="3" t="n">
-        <v>9980.713</v>
+        <v>12338.605</v>
       </c>
       <c r="AO17" s="3" t="n">
-        <v>11284.046</v>
+        <v>13269</v>
       </c>
       <c r="AP17" s="3" t="n">
-        <v>126511.1630773044</v>
+        <v>141599.0549680233</v>
       </c>
       <c r="AQ17" s="3" t="n">
-        <v>126460.9732010443</v>
+        <v>141666.3057069586</v>
       </c>
     </row>
     <row r="18">
@@ -3608,12 +3617,12 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>STRICT</t>
+          <t>NONSTRICT</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>CAND_001</t>
+          <t>CAND_006</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3643,73 +3652,73 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>19-07-2026</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19-07-2026</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>19-07-2026</t>
+          <t>17-07-2026_to_19-07-2026</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_017_STRICT_Chennai_to_Pondicherry.xlsx</t>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_017_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>verified_bdff61acc7fcadf8</t>
+          <t>verified_bc64c4f5f8b414f6</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>verified_49abd2a79268e808</t>
+          <t>verified_1054093294ed2491</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19 09:18:36.867518</t>
+          <t>2026-07-17 07:59:53.804941229</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19 12:34:01.000000</t>
+          <t>2026-07-17 11:39:50.000000000</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19 11:08:45.000000</t>
+          <t>2026-07-19 11:08:45.000000000</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2026-07-19 15:35:36.793285</t>
+          <t>2026-07-19 15:37:58.000000000</t>
         </is>
       </c>
       <c r="T18" s="2" t="n">
-        <v>145.9064422742783</v>
+        <v>146.1177802267275</v>
       </c>
       <c r="U18" s="2" t="n">
-        <v>145.9943306994583</v>
+        <v>146.2265476173814</v>
       </c>
       <c r="V18" s="2" t="n">
-        <v>0.0878884251799263</v>
+        <v>0.1087673906538384</v>
       </c>
       <c r="W18" s="2" t="n">
-        <v>0.0602361512007205</v>
+        <v>0.074438162477603</v>
       </c>
       <c r="X18" s="2" t="n">
-        <v>2.918128845485567</v>
+        <v>2.922355604534551</v>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
@@ -3717,25 +3726,25 @@
         </is>
       </c>
       <c r="Z18" s="2" t="n">
-        <v>145.9262625330926</v>
+        <v>146.1684997136095</v>
       </c>
       <c r="AA18" s="2" t="n">
         <v>1</v>
       </c>
       <c r="AB18" s="2" t="n">
-        <v>0.998342753869736</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="2" t="n">
-        <v>13.00879632340491</v>
+        <v>13.00872658647151</v>
       </c>
       <c r="AD18" s="2" t="n">
-        <v>80.2108498893635</v>
+        <v>80.21065041741409</v>
       </c>
       <c r="AE18" s="2" t="n">
-        <v>11.93263855330246</v>
+        <v>11.93232</v>
       </c>
       <c r="AF18" s="2" t="n">
-        <v>79.81293541312591</v>
+        <v>79.81483499999999</v>
       </c>
       <c r="AG18" s="2" t="inlineStr">
         <is>
@@ -3749,36 +3758,36 @@
       </c>
       <c r="AI18" s="2" t="inlineStr">
         <is>
-          <t>PAIR_017 | STRICT | Chennai to Pondicherry</t>
+          <t>PAIR_017 | NONSTRICT | Chennai to Pondicherry</t>
         </is>
       </c>
       <c r="AJ18" s="2" t="inlineStr">
         <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
         </is>
       </c>
       <c r="AK18" s="2" t="inlineStr">
         <is>
-          <t>13-09-2026 17:51:55</t>
+          <t>29-09-2026 12:15:26</t>
         </is>
       </c>
       <c r="AL18" s="2" t="n">
-        <v>1118</v>
+        <v>1142</v>
       </c>
       <c r="AM18" s="2" t="n">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="AN18" s="2" t="n">
-        <v>11724.132</v>
+        <v>13196.195</v>
       </c>
       <c r="AO18" s="2" t="n">
-        <v>16011.793</v>
+        <v>16153</v>
       </c>
       <c r="AP18" s="2" t="n">
-        <v>145906.4422742808</v>
+        <v>146117.7802267258</v>
       </c>
       <c r="AQ18" s="2" t="n">
-        <v>145994.3306994593</v>
+        <v>146226.5476173816</v>
       </c>
     </row>
     <row r="19">
@@ -3789,181 +3798,3801 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>CAND_004</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2026_to_19-07-2026</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_19-07-2026\PAIR_018_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>verified_15412510a4af5bed</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>verified_1ce33d8c8868f78e</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:26:56.323520580</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:33:03.257434725</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:43:51.000000000</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:25:00.000000000</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="n">
+        <v>141.7178099447914</v>
+      </c>
+      <c r="U19" s="2" t="n">
+        <v>141.7137294264354</v>
+      </c>
+      <c r="V19" s="2" t="n">
+        <v>0.0040805183560621</v>
+      </c>
+      <c r="W19" s="2" t="n">
+        <v>0.0028794093363977</v>
+      </c>
+      <c r="X19" s="2" t="n">
+        <v>2.834274588528708</v>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="n">
+        <v>141.6377285485467</v>
+      </c>
+      <c r="AA19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="2" t="n">
+        <v>13.00724677951333</v>
+      </c>
+      <c r="AD19" s="2" t="n">
+        <v>80.23829613187164</v>
+      </c>
+      <c r="AE19" s="2" t="n">
+        <v>11.93202161710183</v>
+      </c>
+      <c r="AF19" s="2" t="n">
+        <v>79.80778733363579</v>
+      </c>
+      <c r="AG19" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH19" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI19" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_018 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ19" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK19" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:26</t>
+        </is>
+      </c>
+      <c r="AL19" s="2" t="n">
+        <v>1073</v>
+      </c>
+      <c r="AM19" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AN19" s="2" t="n">
+        <v>11166.933</v>
+      </c>
+      <c r="AO19" s="2" t="n">
+        <v>13269</v>
+      </c>
+      <c r="AP19" s="2" t="n">
+        <v>141717.8099447946</v>
+      </c>
+      <c r="AQ19" s="2" t="n">
+        <v>141713.7294264383</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_019</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>CAND_009</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2026</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>17-07-2026_to_25-09-2026</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\17-07-2026_to_25-09-2026\PAIR_019_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>verified_857b5a523fbbfc53</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>verified_1ce33d8c8868f78e</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 14:13:59.699076451</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 17:55:07.045032255</t>
+        </is>
+      </c>
+      <c r="R20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 11:43:51.000000000</t>
+        </is>
+      </c>
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-17 15:25:00.000000000</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="n">
+        <v>141.8622317088206</v>
+      </c>
+      <c r="U20" s="2" t="n">
+        <v>141.6733980516029</v>
+      </c>
+      <c r="V20" s="2" t="n">
+        <v>0.1888336572177422</v>
+      </c>
+      <c r="W20" s="2" t="n">
+        <v>0.1332880130036563</v>
+      </c>
+      <c r="X20" s="2" t="n">
+        <v>2.833467961032058</v>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="n">
+        <v>141.6377285485467</v>
+      </c>
+      <c r="AA20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="2" t="n">
+        <v>13.00723980554129</v>
+      </c>
+      <c r="AD20" s="2" t="n">
+        <v>80.23826407875838</v>
+      </c>
+      <c r="AE20" s="2" t="n">
+        <v>11.93239575562487</v>
+      </c>
+      <c r="AF20" s="2" t="n">
+        <v>79.80763818328134</v>
+      </c>
+      <c r="AG20" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH20" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI20" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_019 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ20" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK20" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:27</t>
+        </is>
+      </c>
+      <c r="AL20" s="2" t="n">
+        <v>2119</v>
+      </c>
+      <c r="AM20" s="2" t="n">
+        <v>1024</v>
+      </c>
+      <c r="AN20" s="2" t="n">
+        <v>13267.346</v>
+      </c>
+      <c r="AO20" s="2" t="n">
+        <v>13269</v>
+      </c>
+      <c r="AP20" s="2" t="n">
+        <v>141862.2317088252</v>
+      </c>
+      <c r="AQ20" s="2" t="n">
+        <v>141673.3980516045</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_020</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
           <t>STRICT</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>CAND_012</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>CAND_022</t>
+        </is>
+      </c>
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>Pondicherry to Chennai</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="3" t="inlineStr">
         <is>
           <t>COMMON_ROUTE_SEGMENT_TAT</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="3" t="inlineStr">
         <is>
           <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G21" s="3" t="inlineStr">
         <is>
           <t>PASSED</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="H21" s="3" t="inlineStr">
         <is>
           <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
+      <c r="I21" s="3" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="L21" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026\PAIR_020_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
+          <t>verified_09767f5cfc6bbb35</t>
+        </is>
+      </c>
+      <c r="O21" s="3" t="inlineStr">
+        <is>
+          <t>verified_5a4bc25af139b115</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:14:38.786008121</t>
+        </is>
+      </c>
+      <c r="Q21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:19:31.142914227</t>
+        </is>
+      </c>
+      <c r="R21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:20:34.000000000</t>
+        </is>
+      </c>
+      <c r="S21" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:30:23.423595809</t>
+        </is>
+      </c>
+      <c r="T21" s="3" t="n">
+        <v>126.7971112808863</v>
+      </c>
+      <c r="U21" s="3" t="n">
+        <v>126.7676219192401</v>
+      </c>
+      <c r="V21" s="3" t="n">
+        <v>0.0294893616461848</v>
+      </c>
+      <c r="W21" s="3" t="n">
+        <v>0.0232625343914486</v>
+      </c>
+      <c r="X21" s="3" t="n">
+        <v>2.535352438384801</v>
+      </c>
+      <c r="Y21" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v>126.7243169954536</v>
+      </c>
+      <c r="AA21" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="3" t="n">
+        <v>0.9192795196797864</v>
+      </c>
+      <c r="AC21" s="3" t="n">
+        <v>11.94061995370101</v>
+      </c>
+      <c r="AD21" s="3" t="n">
+        <v>79.80822044753046</v>
+      </c>
+      <c r="AE21" s="3" t="n">
+        <v>12.89809640493977</v>
+      </c>
+      <c r="AF21" s="3" t="n">
+        <v>80.24542875618252</v>
+      </c>
+      <c r="AG21" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH21" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI21" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_020 | STRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ21" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK21" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:28</t>
+        </is>
+      </c>
+      <c r="AL21" s="3" t="n">
+        <v>979</v>
+      </c>
+      <c r="AM21" s="3" t="n">
+        <v>992</v>
+      </c>
+      <c r="AN21" s="3" t="n">
+        <v>11092.357</v>
+      </c>
+      <c r="AO21" s="3" t="n">
+        <v>11389.424</v>
+      </c>
+      <c r="AP21" s="3" t="n">
+        <v>126797.111280885</v>
+      </c>
+      <c r="AQ21" s="3" t="n">
+        <v>126767.6219192398</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_021</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>CAND_025</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>20-07-2026</t>
         </is>
       </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026_to_20-07-2026</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_021_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>verified_09767f5cfc6bbb35</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>verified_f4d3e9223e856e32</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 14:59:13.286758739</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:18:32.519256376</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:56:44.000000000</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 19:26:14.650937403</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="n">
+        <v>106.7510397234517</v>
+      </c>
+      <c r="U22" s="2" t="n">
+        <v>106.7303536725832</v>
+      </c>
+      <c r="V22" s="2" t="n">
+        <v>0.0206860508684911</v>
+      </c>
+      <c r="W22" s="2" t="n">
+        <v>0.0193816006006593</v>
+      </c>
+      <c r="X22" s="2" t="n">
+        <v>2.134607073451664</v>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="n">
+        <v>106.6887709766038</v>
+      </c>
+      <c r="AA22" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="2" t="n">
+        <v>0.8418945963975984</v>
+      </c>
+      <c r="AC22" s="2" t="n">
+        <v>12.09212293338802</v>
+      </c>
+      <c r="AD22" s="2" t="n">
+        <v>79.89393395207165</v>
+      </c>
+      <c r="AE22" s="2" t="n">
+        <v>12.89737507024662</v>
+      </c>
+      <c r="AF22" s="2" t="n">
+        <v>80.24725579534282</v>
+      </c>
+      <c r="AG22" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH22" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI22" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_021 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ22" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK22" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:28</t>
+        </is>
+      </c>
+      <c r="AL22" s="2" t="n">
+        <v>830</v>
+      </c>
+      <c r="AM22" s="2" t="n">
+        <v>804</v>
+      </c>
+      <c r="AN22" s="2" t="n">
+        <v>8359.232</v>
+      </c>
+      <c r="AO22" s="2" t="n">
+        <v>8970.651</v>
+      </c>
+      <c r="AP22" s="2" t="n">
+        <v>106751.0397234517</v>
+      </c>
+      <c r="AQ22" s="2" t="n">
+        <v>106730.3536725813</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_022</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>CAND_024</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>20-07-2026</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026_to_20-07-2026</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_20-07-2026\PAIR_022_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>verified_fdd276bba7af4ffb</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>verified_5a4bc25af139b115</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:14:55.177888204</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 17:01:15.891391818</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:20:34.000000000</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 19:28:38.045576935</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="n">
+        <v>126.5111630773056</v>
+      </c>
+      <c r="U23" s="2" t="n">
+        <v>126.460973201046</v>
+      </c>
+      <c r="V23" s="2" t="n">
+        <v>0.0501898762595942</v>
+      </c>
+      <c r="W23" s="2" t="n">
+        <v>0.0396880357545588</v>
+      </c>
+      <c r="X23" s="2" t="n">
+        <v>2.52921946402092</v>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="n">
+        <v>126.44842951288</v>
+      </c>
+      <c r="AA23" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="2" t="n">
+        <v>0.9172781854569714</v>
+      </c>
+      <c r="AC23" s="2" t="n">
+        <v>11.94079973611527</v>
+      </c>
+      <c r="AD23" s="2" t="n">
+        <v>79.80825475984354</v>
+      </c>
+      <c r="AE23" s="2" t="n">
+        <v>12.89692247679694</v>
+      </c>
+      <c r="AF23" s="2" t="n">
+        <v>80.24722803800822</v>
+      </c>
+      <c r="AG23" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH23" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI23" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_022 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ23" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK23" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:29</t>
+        </is>
+      </c>
+      <c r="AL23" s="2" t="n">
+        <v>983</v>
+      </c>
+      <c r="AM23" s="2" t="n">
+        <v>988</v>
+      </c>
+      <c r="AN23" s="2" t="n">
+        <v>9980.713</v>
+      </c>
+      <c r="AO23" s="2" t="n">
+        <v>11284.046</v>
+      </c>
+      <c r="AP23" s="2" t="n">
+        <v>126511.1630773044</v>
+      </c>
+      <c r="AQ23" s="2" t="n">
+        <v>126460.9732010443</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_023</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>CAND_031</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>18-07-2026_to_26-09-2026</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\18-07-2026_to_26-09-2026\PAIR_023_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>verified_2ef63d7709cb5e84</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>verified_5a4bc25af139b115</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 14:31:24.552784178</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:43:26.486809471</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 16:20:34.000000000</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-18 17:41:38.397074240</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="n">
+        <v>44.15970146038063</v>
+      </c>
+      <c r="U24" s="2" t="n">
+        <v>44.07790624114247</v>
+      </c>
+      <c r="V24" s="2" t="n">
+        <v>0.08179521923816679</v>
+      </c>
+      <c r="W24" s="2" t="n">
+        <v>0.1855696565773327</v>
+      </c>
+      <c r="X24" s="2" t="n">
+        <v>0.8815581248228493</v>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="n">
+        <v>44.05003471757784</v>
+      </c>
+      <c r="AA24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="2" t="n">
+        <v>0.3195463642428286</v>
+      </c>
+      <c r="AC24" s="2" t="n">
+        <v>11.94083487528801</v>
+      </c>
+      <c r="AD24" s="2" t="n">
+        <v>79.80825776392089</v>
+      </c>
+      <c r="AE24" s="2" t="n">
+        <v>12.27739642985086</v>
+      </c>
+      <c r="AF24" s="2" t="n">
+        <v>79.98360542525798</v>
+      </c>
+      <c r="AG24" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH24" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI24" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_023 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK24" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:29</t>
+        </is>
+      </c>
+      <c r="AL24" s="2" t="n">
+        <v>664</v>
+      </c>
+      <c r="AM24" s="2" t="n">
+        <v>328</v>
+      </c>
+      <c r="AN24" s="2" t="n">
+        <v>4321.934</v>
+      </c>
+      <c r="AO24" s="2" t="n">
+        <v>4864.397</v>
+      </c>
+      <c r="AP24" s="2" t="n">
+        <v>44159.70146038075</v>
+      </c>
+      <c r="AQ24" s="2" t="n">
+        <v>44077.90624114242</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_024</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>CAND_001</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G25" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H25" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I25" s="3" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026\PAIR_024_STRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>verified_15412510a4af5bed</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t>verified_1054093294ed2491</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-19 09:18:36.867518404</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-19 12:34:01.000000000</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:08:45.000000000</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:35:36.793285674</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>145.9064422742783</v>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v>145.9943306994583</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.0878884251799263</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.0602361512007205</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>2.918128845485567</v>
+      </c>
+      <c r="Y25" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>145.9262625330926</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.998342753869736</v>
+      </c>
+      <c r="AC25" s="3" t="n">
+        <v>13.00879632340491</v>
+      </c>
+      <c r="AD25" s="3" t="n">
+        <v>80.2108498893635</v>
+      </c>
+      <c r="AE25" s="3" t="n">
+        <v>11.93263855330246</v>
+      </c>
+      <c r="AF25" s="3" t="n">
+        <v>79.81293541312591</v>
+      </c>
+      <c r="AG25" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH25" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI25" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_024 | STRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ25" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK25" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:29</t>
+        </is>
+      </c>
+      <c r="AL25" s="3" t="n">
+        <v>1118</v>
+      </c>
+      <c r="AM25" s="3" t="n">
+        <v>1115</v>
+      </c>
+      <c r="AN25" s="3" t="n">
+        <v>11724.132</v>
+      </c>
+      <c r="AO25" s="3" t="n">
+        <v>16011.793</v>
+      </c>
+      <c r="AP25" s="3" t="n">
+        <v>145906.4422742808</v>
+      </c>
+      <c r="AQ25" s="3" t="n">
+        <v>145994.3306994593</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_025</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>CAND_008</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>FULL_ROUTE_TAT_ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25-09-2026</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>19-07-2026</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>19-07-2026_to_25-09-2026</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\19-07-2026_to_25-09-2026\PAIR_025_NONSTRICT_Chennai_to_Pondicherry.xlsx</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>verified_857b5a523fbbfc53</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>verified_1054093294ed2491</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 13:56:09.759414496</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-25 18:11:54.391881685</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 11:08:45.000000000</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-19 15:34:22.798805861</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="n">
+        <v>146.0112624287633</v>
+      </c>
+      <c r="U26" s="2" t="n">
+        <v>145.8893363990335</v>
+      </c>
+      <c r="V26" s="2" t="n">
+        <v>0.1219260297298205</v>
+      </c>
+      <c r="W26" s="2" t="n">
+        <v>0.08357432608805</v>
+      </c>
+      <c r="X26" s="2" t="n">
+        <v>2.91778672798067</v>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="n">
+        <v>145.875967692835</v>
+      </c>
+      <c r="AA26" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="2" t="n">
+        <v>0.9979986657771848</v>
+      </c>
+      <c r="AC26" s="2" t="n">
+        <v>13.00868139121744</v>
+      </c>
+      <c r="AD26" s="2" t="n">
+        <v>80.21063313599433</v>
+      </c>
+      <c r="AE26" s="2" t="n">
+        <v>11.93255386642905</v>
+      </c>
+      <c r="AF26" s="2" t="n">
+        <v>79.81175264707703</v>
+      </c>
+      <c r="AG26" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH26" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI26" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_025 | NONSTRICT | Chennai to Pondicherry</t>
+        </is>
+      </c>
+      <c r="AJ26" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK26" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:30</t>
+        </is>
+      </c>
+      <c r="AL26" s="2" t="n">
+        <v>2242</v>
+      </c>
+      <c r="AM26" s="2" t="n">
+        <v>1114</v>
+      </c>
+      <c r="AN26" s="2" t="n">
+        <v>15344.633</v>
+      </c>
+      <c r="AO26" s="2" t="n">
+        <v>15937.799</v>
+      </c>
+      <c r="AP26" s="2" t="n">
+        <v>146011.262428766</v>
+      </c>
+      <c r="AQ26" s="2" t="n">
+        <v>145889.3363990339</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_026</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>CAND_021</t>
+        </is>
+      </c>
+      <c r="D27" s="3" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t>20-07-2026</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>D:\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_018_STRICT_Pondicherry_to_Chennai.xlsx</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>verified_2e8f3bf6137add72</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>verified_b6771ff18a5dc98d</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20 14:51:18.364690</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20 17:58:57.541852</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20 16:56:44.000000</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20 20:11:41.503875</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="n">
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026\PAIR_026_STRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
+          <t>verified_fdd276bba7af4ffb</t>
+        </is>
+      </c>
+      <c r="O27" s="3" t="inlineStr">
+        <is>
+          <t>verified_f4d3e9223e856e32</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 14:51:18.364690127</t>
+        </is>
+      </c>
+      <c r="Q27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 17:58:57.541852526</t>
+        </is>
+      </c>
+      <c r="R27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 16:56:44.000000000</t>
+        </is>
+      </c>
+      <c r="S27" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20 20:11:41.503875467</t>
+        </is>
+      </c>
+      <c r="T27" s="3" t="n">
         <v>123.9926446469663</v>
       </c>
-      <c r="U19" s="2" t="n">
+      <c r="U27" s="3" t="n">
         <v>123.9802750677116</v>
       </c>
-      <c r="V19" s="2" t="n">
+      <c r="V27" s="3" t="n">
         <v>0.0123695792546811</v>
       </c>
-      <c r="W19" s="2" t="n">
+      <c r="W27" s="3" t="n">
         <v>0.009977054211184401</v>
       </c>
-      <c r="X19" s="2" t="n">
+      <c r="X27" s="3" t="n">
         <v>2.479605501354232</v>
       </c>
-      <c r="Y19" s="2" t="inlineStr">
+      <c r="Y27" s="3" t="inlineStr">
         <is>
           <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
         </is>
       </c>
-      <c r="Z19" s="2" t="n">
+      <c r="Z27" s="3" t="n">
         <v>123.934816364264</v>
       </c>
-      <c r="AA19" s="2" t="n">
+      <c r="AA27" s="3" t="n">
         <v>0.9986366734832992</v>
       </c>
-      <c r="AB19" s="2" t="n">
+      <c r="AB27" s="3" t="n">
         <v>0.9779853235490328</v>
       </c>
-      <c r="AC19" s="2" t="n">
+      <c r="AC27" s="3" t="n">
         <v>12.09211538720332</v>
       </c>
-      <c r="AD19" s="2" t="n">
+      <c r="AD27" s="3" t="n">
         <v>79.89393892911241</v>
       </c>
-      <c r="AE19" s="2" t="n">
+      <c r="AE27" s="3" t="n">
         <v>13.00894670488603</v>
       </c>
-      <c r="AF19" s="2" t="n">
+      <c r="AF27" s="3" t="n">
         <v>80.21177578423934</v>
       </c>
-      <c r="AG19" s="2" t="inlineStr">
+      <c r="AG27" s="3" t="inlineStr">
         <is>
           <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
         </is>
       </c>
-      <c r="AH19" s="2" t="inlineStr">
+      <c r="AH27" s="3" t="inlineStr">
         <is>
           <t>COMPLETED</t>
         </is>
       </c>
-      <c r="AI19" s="2" t="inlineStr">
-        <is>
-          <t>PAIR_018 | STRICT | Pondicherry to Chennai</t>
-        </is>
-      </c>
-      <c r="AJ19" s="2" t="inlineStr">
-        <is>
-          <t>2026-08-06_STAGE_3_PRESERVE_ADDRESS_V2</t>
-        </is>
-      </c>
-      <c r="AK19" s="2" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:51:59</t>
-        </is>
-      </c>
-      <c r="AL19" s="2" t="n">
+      <c r="AI27" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_026 | STRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ27" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK27" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:31</t>
+        </is>
+      </c>
+      <c r="AL27" s="3" t="n">
         <v>1002</v>
       </c>
-      <c r="AM19" s="2" t="n">
+      <c r="AM27" s="3" t="n">
         <v>950</v>
       </c>
-      <c r="AN19" s="2" t="n">
+      <c r="AN27" s="3" t="n">
         <v>11259.177</v>
       </c>
-      <c r="AO19" s="2" t="n">
+      <c r="AO27" s="3" t="n">
         <v>11697.504</v>
       </c>
-      <c r="AP19" s="2" t="n">
+      <c r="AP27" s="3" t="n">
         <v>123992.6446469637</v>
       </c>
-      <c r="AQ19" s="2" t="n">
+      <c r="AQ27" s="3" t="n">
         <v>123980.2750677086</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_027</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>CAND_035</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026_to_29-07-2026</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_29-07-2026\PAIR_027_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>verified_6417676c32019437</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>verified_885e07a3434192f0</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:03:01.256843935</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 00:42:59.808273418</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 22:59:49.062441416</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:23:33.647364376</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="n">
+        <v>14.82892455320732</v>
+      </c>
+      <c r="U28" s="2" t="n">
+        <v>15.14287648205785</v>
+      </c>
+      <c r="V28" s="2" t="n">
+        <v>0.3139519288505283</v>
+      </c>
+      <c r="W28" s="2" t="n">
+        <v>2.117159121850305</v>
+      </c>
+      <c r="X28" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="n">
+        <v>14.74783260218571</v>
+      </c>
+      <c r="AA28" s="2" t="n">
+        <v>0.9857142857142858</v>
+      </c>
+      <c r="AB28" s="2" t="n">
+        <v>0.0453635757171447</v>
+      </c>
+      <c r="AC28" s="2" t="n">
+        <v>12.89969823937384</v>
+      </c>
+      <c r="AD28" s="2" t="n">
+        <v>77.63337591352393</v>
+      </c>
+      <c r="AE28" s="2" t="n">
+        <v>12.79871332144761</v>
+      </c>
+      <c r="AF28" s="2" t="n">
+        <v>77.71650701351723</v>
+      </c>
+      <c r="AG28" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH28" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI28" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_027 | NONSTRICT | SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ28" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK28" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:31</t>
+        </is>
+      </c>
+      <c r="AL28" s="2" t="n">
+        <v>103</v>
+      </c>
+      <c r="AM28" s="2" t="n">
+        <v>117</v>
+      </c>
+      <c r="AN28" s="2" t="n">
+        <v>2398.551</v>
+      </c>
+      <c r="AO28" s="2" t="n">
+        <v>1424.585</v>
+      </c>
+      <c r="AP28" s="2" t="n">
+        <v>14828.92455320712</v>
+      </c>
+      <c r="AQ28" s="2" t="n">
+        <v>15142.87648205564</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_028</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>CAND_039</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026_to_05-09-2026</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_05-09-2026\PAIR_028_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>verified_6417676c32019437</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>verified_446af55348030fd8</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 02:02:59.590543708</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 02:23:15.353768118</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 01:04:39.809861003</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 01:24:29.946242573</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="n">
+        <v>22.49736924507095</v>
+      </c>
+      <c r="U29" s="2" t="n">
+        <v>22.45363674285575</v>
+      </c>
+      <c r="V29" s="2" t="n">
+        <v>0.0437325022151995</v>
+      </c>
+      <c r="W29" s="2" t="n">
+        <v>0.194768013378119</v>
+      </c>
+      <c r="X29" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="n">
+        <v>22.35481486189393</v>
+      </c>
+      <c r="AA29" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" s="2" t="n">
+        <v>0.0693795863909272</v>
+      </c>
+      <c r="AC29" s="2" t="n">
+        <v>12.55257221819525</v>
+      </c>
+      <c r="AD29" s="2" t="n">
+        <v>78.19009563697669</v>
+      </c>
+      <c r="AE29" s="2" t="n">
+        <v>12.55241851629008</v>
+      </c>
+      <c r="AF29" s="2" t="n">
+        <v>78.34961153120346</v>
+      </c>
+      <c r="AG29" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH29" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI29" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_028 | NONSTRICT | SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ29" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK29" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:31</t>
+        </is>
+      </c>
+      <c r="AL29" s="2" t="n">
+        <v>186</v>
+      </c>
+      <c r="AM29" s="2" t="n">
+        <v>242</v>
+      </c>
+      <c r="AN29" s="2" t="n">
+        <v>1215.763</v>
+      </c>
+      <c r="AO29" s="2" t="n">
+        <v>1190.136</v>
+      </c>
+      <c r="AP29" s="2" t="n">
+        <v>22497.36924506911</v>
+      </c>
+      <c r="AQ29" s="2" t="n">
+        <v>22453.63674285611</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_029</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>CAND_030</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>26-09-2026</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>20-07-2026_to_26-09-2026</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-07-2026_to_26-09-2026\PAIR_029_NONSTRICT_Pondicherry_to_Chennai.xlsx</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>verified_2ef63d7709cb5e84</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>verified_f4d3e9223e856e32</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 15:48:40.974630505</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-26 16:31:32.517784607</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 17:49:35.649884775</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20 18:35:05.068490165</t>
+        </is>
+      </c>
+      <c r="T30" s="2" t="n">
+        <v>34.46653823125065</v>
+      </c>
+      <c r="U30" s="2" t="n">
+        <v>34.32677600023345</v>
+      </c>
+      <c r="V30" s="2" t="n">
+        <v>0.1397622310171939</v>
+      </c>
+      <c r="W30" s="2" t="n">
+        <v>0.4071522213919637</v>
+      </c>
+      <c r="X30" s="2" t="n">
+        <v>0.686535520004669</v>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="n">
+        <v>34.32301189897078</v>
+      </c>
+      <c r="AA30" s="2" t="n">
+        <v>0.995085995085995</v>
+      </c>
+      <c r="AB30" s="2" t="n">
+        <v>0.2708472314876584</v>
+      </c>
+      <c r="AC30" s="2" t="n">
+        <v>12.30283957303532</v>
+      </c>
+      <c r="AD30" s="2" t="n">
+        <v>80.01211700158352</v>
+      </c>
+      <c r="AE30" s="2" t="n">
+        <v>12.54652938090469</v>
+      </c>
+      <c r="AF30" s="2" t="n">
+        <v>80.14277103397315</v>
+      </c>
+      <c r="AG30" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH30" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI30" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_029 | NONSTRICT | Pondicherry to Chennai</t>
+        </is>
+      </c>
+      <c r="AJ30" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK30" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:31</t>
+        </is>
+      </c>
+      <c r="AL30" s="2" t="n">
+        <v>547</v>
+      </c>
+      <c r="AM30" s="2" t="n">
+        <v>251</v>
+      </c>
+      <c r="AN30" s="2" t="n">
+        <v>2571.543</v>
+      </c>
+      <c r="AO30" s="2" t="n">
+        <v>2729.418</v>
+      </c>
+      <c r="AP30" s="2" t="n">
+        <v>34466.53823125114</v>
+      </c>
+      <c r="AQ30" s="2" t="n">
+        <v>34326.77600023323</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_030</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>CAND_038</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>29-07-2026</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>29-07-2026_to_06-09-2026</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\29-07-2026_to_06-09-2026\PAIR_030_NONSTRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>verified_fd1670a3e073c823</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>verified_885e07a3434192f0</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:48:04.367453943</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:39:51.000000000</t>
+        </is>
+      </c>
+      <c r="R31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-29 23:36:23.253979873</t>
+        </is>
+      </c>
+      <c r="S31" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-30 03:10:17.184562455</t>
+        </is>
+      </c>
+      <c r="T31" s="2" t="n">
+        <v>231.4242273523425</v>
+      </c>
+      <c r="U31" s="2" t="n">
+        <v>231.4429858569087</v>
+      </c>
+      <c r="V31" s="2" t="n">
+        <v>0.0187585045661649</v>
+      </c>
+      <c r="W31" s="2" t="n">
+        <v>0.0081056788136555</v>
+      </c>
+      <c r="X31" s="2" t="n">
+        <v>4.628484547046851</v>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="n">
+        <v>231.4278325023623</v>
+      </c>
+      <c r="AA31" s="2" t="n">
+        <v>0.9023689877961236</v>
+      </c>
+      <c r="AB31" s="2" t="n">
+        <v>0.9286167006347524</v>
+      </c>
+      <c r="AC31" s="2" t="n">
+        <v>12.79239829135291</v>
+      </c>
+      <c r="AD31" s="2" t="n">
+        <v>77.72817338096201</v>
+      </c>
+      <c r="AE31" s="2" t="n">
+        <v>12.89835073824982</v>
+      </c>
+      <c r="AF31" s="2" t="n">
+        <v>79.54325993274523</v>
+      </c>
+      <c r="AG31" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH31" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI31" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_030 | NONSTRICT | SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ31" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK31" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:32</t>
+        </is>
+      </c>
+      <c r="AL31" s="2" t="n">
+        <v>824</v>
+      </c>
+      <c r="AM31" s="2" t="n">
+        <v>1852</v>
+      </c>
+      <c r="AN31" s="2" t="n">
+        <v>13906.633</v>
+      </c>
+      <c r="AO31" s="2" t="n">
+        <v>12833.931</v>
+      </c>
+      <c r="AP31" s="2" t="n">
+        <v>231424.2273523428</v>
+      </c>
+      <c r="AQ31" s="2" t="n">
+        <v>231442.9858569063</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_031</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>CAND_016</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to SilkBoard</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>04-09-2026</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>31-07-2026</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>31-07-2026_to_04-09-2026</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\31-07-2026_to_04-09-2026\PAIR_031_NONSTRICT_Madhuravoyal_to_SilkBoard.xlsx</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>verified_aabcbc6d82d2ca79</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>verified_f8d0549d30ce15f8</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05 01:04:25.339161703</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-05 01:19:18.066584652</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:13:45.997837347</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-01 00:30:31.384687026</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="n">
+        <v>12.73848083938355</v>
+      </c>
+      <c r="U32" s="2" t="n">
+        <v>12.73857342260521</v>
+      </c>
+      <c r="V32" s="2" t="n">
+        <v>9.258322166338928e-05</v>
+      </c>
+      <c r="W32" s="2" t="n">
+        <v>0.0007267995519304</v>
+      </c>
+      <c r="X32" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="n">
+        <v>12.64016602610399</v>
+      </c>
+      <c r="AA32" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" s="2" t="n">
+        <v>0.038692461641094</v>
+      </c>
+      <c r="AC32" s="2" t="n">
+        <v>12.91444665460259</v>
+      </c>
+      <c r="AD32" s="2" t="n">
+        <v>79.85706791632448</v>
+      </c>
+      <c r="AE32" s="2" t="n">
+        <v>12.87415436515486</v>
+      </c>
+      <c r="AF32" s="2" t="n">
+        <v>79.75045482557009</v>
+      </c>
+      <c r="AG32" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_031 | NONSTRICT | Madhuravoyal to SilkBoard</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:32</t>
+        </is>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="AM32" s="2" t="n">
+        <v>118</v>
+      </c>
+      <c r="AN32" s="2" t="n">
+        <v>892.7280000000001</v>
+      </c>
+      <c r="AO32" s="2" t="n">
+        <v>1005.387</v>
+      </c>
+      <c r="AP32" s="2" t="n">
+        <v>12738.48083938423</v>
+      </c>
+      <c r="AQ32" s="2" t="n">
+        <v>12738.57342260571</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_032</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>CAND_034</t>
+        </is>
+      </c>
+      <c r="D33" s="3" t="inlineStr">
+        <is>
+          <t>SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G33" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H33" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I33" s="3" t="inlineStr">
+        <is>
+          <t>06-09-2026</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2026</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>05-09-2026_to_06-09-2026</t>
+        </is>
+      </c>
+      <c r="L33" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\05-09-2026_to_06-09-2026\PAIR_032_STRICT_SilkBoard_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t>verified_fd1670a3e073c823</t>
+        </is>
+      </c>
+      <c r="O33" s="3" t="inlineStr">
+        <is>
+          <t>verified_446af55348030fd8</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06 00:27:57.642119293</t>
+        </is>
+      </c>
+      <c r="Q33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06 04:39:51.000000000</t>
+        </is>
+      </c>
+      <c r="R33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-05 23:26:13.958806165</t>
+        </is>
+      </c>
+      <c r="S33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-06 03:20:51.458409604</t>
+        </is>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>240.4425765887824</v>
+      </c>
+      <c r="U33" s="3" t="n">
+        <v>240.727583098502</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0.2850065097195795</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0.1185341272594215</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>4.808851531775648</v>
+      </c>
+      <c r="Y33" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>240.406252174318</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0.926744989633725</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0.9646430953969312</v>
+      </c>
+      <c r="AC33" s="3" t="n">
+        <v>12.8458745553374</v>
+      </c>
+      <c r="AD33" s="3" t="n">
+        <v>77.67269053607896</v>
+      </c>
+      <c r="AE33" s="3" t="n">
+        <v>12.89841383363842</v>
+      </c>
+      <c r="AF33" s="3" t="n">
+        <v>79.54357271710452</v>
+      </c>
+      <c r="AG33" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH33" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI33" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_032 | STRICT | SilkBoard to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ33" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK33" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:33</t>
+        </is>
+      </c>
+      <c r="AL33" s="3" t="n">
+        <v>884</v>
+      </c>
+      <c r="AM33" s="3" t="n">
+        <v>2575</v>
+      </c>
+      <c r="AN33" s="3" t="n">
+        <v>15113.358</v>
+      </c>
+      <c r="AO33" s="3" t="n">
+        <v>14077.499</v>
+      </c>
+      <c r="AP33" s="3" t="n">
+        <v>240442.5765887812</v>
+      </c>
+      <c r="AQ33" s="3" t="n">
+        <v>240727.5830985001</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_033</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>CAND_013</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026\PAIR_033_STRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>verified_9b6c02add7efaab5</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>verified_60ea4bf119bd5f88</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:17:00.000000000</t>
+        </is>
+      </c>
+      <c r="Q34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12 02:21:52.853450148</t>
+        </is>
+      </c>
+      <c r="R34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:27:11.000000000</t>
+        </is>
+      </c>
+      <c r="S34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-12 02:36:16.796586734</t>
+        </is>
+      </c>
+      <c r="T34" s="3" t="n">
+        <v>159.817207470761</v>
+      </c>
+      <c r="U34" s="3" t="n">
+        <v>159.5838099715612</v>
+      </c>
+      <c r="V34" s="3" t="n">
+        <v>0.2333974991998104</v>
+      </c>
+      <c r="W34" s="3" t="n">
+        <v>0.146253870766341</v>
+      </c>
+      <c r="X34" s="3" t="n">
+        <v>3.191676199431224</v>
+      </c>
+      <c r="Y34" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z34" s="3" t="n">
+        <v>159.5722159456623</v>
+      </c>
+      <c r="AA34" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" s="3" t="n">
+        <v>0.4889926617745163</v>
+      </c>
+      <c r="AC34" s="3" t="n">
+        <v>13.061225</v>
+      </c>
+      <c r="AD34" s="3" t="n">
+        <v>80.16355</v>
+      </c>
+      <c r="AE34" s="3" t="n">
+        <v>12.8534408431922</v>
+      </c>
+      <c r="AF34" s="3" t="n">
+        <v>78.81745785192851</v>
+      </c>
+      <c r="AG34" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH34" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI34" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_033 | STRICT | Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="AJ34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK34" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:34</t>
+        </is>
+      </c>
+      <c r="AL34" s="3" t="n">
+        <v>1973</v>
+      </c>
+      <c r="AM34" s="3" t="n">
+        <v>647</v>
+      </c>
+      <c r="AN34" s="3" t="n">
+        <v>11092.853</v>
+      </c>
+      <c r="AO34" s="3" t="n">
+        <v>11345.797</v>
+      </c>
+      <c r="AP34" s="3" t="n">
+        <v>159817.2074707596</v>
+      </c>
+      <c r="AQ34" s="3" t="n">
+        <v>159583.80997156</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_034</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>CAND_014</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>11-09-2026</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>18-09-2026</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>11-09-2026_to_18-09-2026</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\11-09-2026_to_18-09-2026\PAIR_034_NONSTRICT_Madhuravoyal_to_Madiwala.xlsx</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>verified_9b6c02add7efaab5</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>verified_5a964e69120cfd90</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11 23:19:37.744182384</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-12 00:25:38.907924214</t>
+        </is>
+      </c>
+      <c r="R35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 17:17:37.516140151</t>
+        </is>
+      </c>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18 18:51:46.476033625</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="n">
+        <v>49.09342708546382</v>
+      </c>
+      <c r="U35" s="2" t="n">
+        <v>49.01363547616133</v>
+      </c>
+      <c r="V35" s="2" t="n">
+        <v>0.0797916093024824</v>
+      </c>
+      <c r="W35" s="2" t="n">
+        <v>0.1627947172808483</v>
+      </c>
+      <c r="X35" s="2" t="n">
+        <v>0.9802727095232266</v>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="n">
+        <v>48.99383595579782</v>
+      </c>
+      <c r="AA35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" s="2" t="n">
+        <v>0.1501000667111407</v>
+      </c>
+      <c r="AC35" s="2" t="n">
+        <v>13.06052534994696</v>
+      </c>
+      <c r="AD35" s="2" t="n">
+        <v>80.15452393992942</v>
+      </c>
+      <c r="AE35" s="2" t="n">
+        <v>12.87607154734569</v>
+      </c>
+      <c r="AF35" s="2" t="n">
+        <v>79.76988414820596</v>
+      </c>
+      <c r="AG35" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_034 | NONSTRICT | Madhuravoyal to Madiwala</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:34</t>
+        </is>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>728</v>
+      </c>
+      <c r="AM35" s="2" t="n">
+        <v>275</v>
+      </c>
+      <c r="AN35" s="2" t="n">
+        <v>3961.164</v>
+      </c>
+      <c r="AO35" s="2" t="n">
+        <v>5648.96</v>
+      </c>
+      <c r="AP35" s="2" t="n">
+        <v>49093.42708546251</v>
+      </c>
+      <c r="AQ35" s="2" t="n">
+        <v>49013.63547616007</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_035</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>CAND_017</t>
+        </is>
+      </c>
+      <c r="D36" s="3" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026\PAIR_035_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t>verified_beddb328b7456fe1</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t>verified_ba92432e63144128</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:07:02.734887323</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:20:12.074096317</t>
+        </is>
+      </c>
+      <c r="R36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:26:26.112279404</t>
+        </is>
+      </c>
+      <c r="S36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:40:28.173618086</t>
+        </is>
+      </c>
+      <c r="T36" s="3" t="n">
+        <v>17.51042605982254</v>
+      </c>
+      <c r="U36" s="3" t="n">
+        <v>17.59592292311555</v>
+      </c>
+      <c r="V36" s="3" t="n">
+        <v>0.0854968632930059</v>
+      </c>
+      <c r="W36" s="3" t="n">
+        <v>0.488262609949723</v>
+      </c>
+      <c r="X36" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y36" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z36" s="3" t="n">
+        <v>17.41189531576211</v>
+      </c>
+      <c r="AA36" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" s="3" t="n">
+        <v>0.0540360240160106</v>
+      </c>
+      <c r="AC36" s="3" t="n">
+        <v>12.91579609911194</v>
+      </c>
+      <c r="AD36" s="3" t="n">
+        <v>79.0584595835744</v>
+      </c>
+      <c r="AE36" s="3" t="n">
+        <v>12.94755626121687</v>
+      </c>
+      <c r="AF36" s="3" t="n">
+        <v>79.21349498846301</v>
+      </c>
+      <c r="AG36" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH36" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI36" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_035 | STRICT | Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ36" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK36" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:34</t>
+        </is>
+      </c>
+      <c r="AL36" s="3" t="n">
+        <v>163</v>
+      </c>
+      <c r="AM36" s="3" t="n">
+        <v>55</v>
+      </c>
+      <c r="AN36" s="3" t="n">
+        <v>789.3389999999999</v>
+      </c>
+      <c r="AO36" s="3" t="n">
+        <v>842.062</v>
+      </c>
+      <c r="AP36" s="3" t="n">
+        <v>17510.42605982269</v>
+      </c>
+      <c r="AQ36" s="3" t="n">
+        <v>17595.92292311513</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_036</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>CAND_019</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>12-09-2026_to_20-09-2026</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_036_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>verified_beddb328b7456fe1</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>verified_dd7dd5fbb1d4fcf8</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:49:31.678820850</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 03:01:14.389061149</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:32:06.077395871</t>
+        </is>
+      </c>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:43:49.981027358</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="n">
+        <v>16.43424965629287</v>
+      </c>
+      <c r="U37" s="2" t="n">
+        <v>16.43868693033091</v>
+      </c>
+      <c r="V37" s="2" t="n">
+        <v>0.0044372740380431</v>
+      </c>
+      <c r="W37" s="2" t="n">
+        <v>0.0270001620447824</v>
+      </c>
+      <c r="X37" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="n">
+        <v>16.33708696293731</v>
+      </c>
+      <c r="AA37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" s="2" t="n">
+        <v>0.0507004669779853</v>
+      </c>
+      <c r="AC37" s="2" t="n">
+        <v>12.53864488040618</v>
+      </c>
+      <c r="AD37" s="2" t="n">
+        <v>78.30629982235928</v>
+      </c>
+      <c r="AE37" s="2" t="n">
+        <v>12.54988528540385</v>
+      </c>
+      <c r="AF37" s="2" t="n">
+        <v>78.44467461399566</v>
+      </c>
+      <c r="AG37" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_036 | NONSTRICT | Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:34</t>
+        </is>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>152</v>
+      </c>
+      <c r="AM37" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="AN37" s="2" t="n">
+        <v>702.71</v>
+      </c>
+      <c r="AO37" s="2" t="n">
+        <v>703.904</v>
+      </c>
+      <c r="AP37" s="2" t="n">
+        <v>16434.24965629278</v>
+      </c>
+      <c r="AQ37" s="2" t="n">
+        <v>16438.68693033036</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_037</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>NONSTRICT</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>CAND_020</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>12-09-2026</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>12-09-2026_to_20-09-2026</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\12-09-2026_to_20-09-2026\PAIR_037_NONSTRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>verified_6976a3c9c0dc9943</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>verified_ba92432e63144128</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:17:59.344252849</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-20 18:14:41.606234889</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 02:45:02.264356383</t>
+        </is>
+      </c>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-13 04:42:50.000000000</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="n">
+        <v>106.476322929305</v>
+      </c>
+      <c r="U38" s="2" t="n">
+        <v>106.4294933713143</v>
+      </c>
+      <c r="V38" s="2" t="n">
+        <v>0.0468295579907476</v>
+      </c>
+      <c r="W38" s="2" t="n">
+        <v>0.0440005458142765</v>
+      </c>
+      <c r="X38" s="2" t="n">
+        <v>2.128589867426286</v>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="n">
+        <v>106.3941498669161</v>
+      </c>
+      <c r="AA38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" s="2" t="n">
+        <v>0.3268845897264842</v>
+      </c>
+      <c r="AC38" s="2" t="n">
+        <v>12.92804763756913</v>
+      </c>
+      <c r="AD38" s="2" t="n">
+        <v>79.26347755383833</v>
+      </c>
+      <c r="AE38" s="2" t="n">
+        <v>13.06148902542309</v>
+      </c>
+      <c r="AF38" s="2" t="n">
+        <v>80.15166334291892</v>
+      </c>
+      <c r="AG38" s="2" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>PAIR_037 | NONSTRICT | Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:35</t>
+        </is>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>1359</v>
+      </c>
+      <c r="AM38" s="2" t="n">
+        <v>408</v>
+      </c>
+      <c r="AN38" s="2" t="n">
+        <v>7002.262</v>
+      </c>
+      <c r="AO38" s="2" t="n">
+        <v>7067.736</v>
+      </c>
+      <c r="AP38" s="2" t="n">
+        <v>106476.3229293066</v>
+      </c>
+      <c r="AQ38" s="2" t="n">
+        <v>106429.493371315</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_038</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>STRICT</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr">
+        <is>
+          <t>CAND_018</t>
+        </is>
+      </c>
+      <c r="D39" s="3" t="inlineStr">
+        <is>
+          <t>Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>COMMON_ROUTE_SEGMENT_TAT</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t>PASSED_ORDERED_ROUTE_VALIDATION</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t>CONTINUOUS_ORDERED_DIRECTION_AWARE_MATCHES</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t>20-09-2026</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>D:\Hameeda_Projects\TAT_MS_INTERCITY\Data\Results\Paired\20-09-2026\PAIR_038_STRICT_Madiwala_to_Madhuravoyal.xlsx</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>verified_6976a3c9c0dc9943</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t>verified_dd7dd5fbb1d4fcf8</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 13:53:57.310090026</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:28:14.925286593</t>
+        </is>
+      </c>
+      <c r="R39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 14:44:32.088845007</t>
+        </is>
+      </c>
+      <c r="S39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-20 16:14:25.762063002</t>
+        </is>
+      </c>
+      <c r="T39" s="3" t="n">
+        <v>118.6528555237146</v>
+      </c>
+      <c r="U39" s="3" t="n">
+        <v>118.3205529638238</v>
+      </c>
+      <c r="V39" s="3" t="n">
+        <v>0.332302559890735</v>
+      </c>
+      <c r="W39" s="3" t="n">
+        <v>0.2808493973082897</v>
+      </c>
+      <c r="X39" s="3" t="n">
+        <v>2.366411059276477</v>
+      </c>
+      <c r="Y39" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_DISTANCES_WITHIN_TOLERANCE</t>
+        </is>
+      </c>
+      <c r="Z39" s="3" t="n">
+        <v>118.3618535740408</v>
+      </c>
+      <c r="AA39" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" s="3" t="n">
+        <v>0.3636540730219945</v>
+      </c>
+      <c r="AC39" s="3" t="n">
+        <v>12.55411015191287</v>
+      </c>
+      <c r="AD39" s="3" t="n">
+        <v>78.45470280676676</v>
+      </c>
+      <c r="AE39" s="3" t="n">
+        <v>12.91202975854729</v>
+      </c>
+      <c r="AF39" s="3" t="n">
+        <v>79.37105123481514</v>
+      </c>
+      <c r="AG39" s="3" t="inlineStr">
+        <is>
+          <t>CROPPED_PAIR_WORKBOOK_CREATED_ALL_RULES_PASSED</t>
+        </is>
+      </c>
+      <c r="AH39" s="3" t="inlineStr">
+        <is>
+          <t>COMPLETED</t>
+        </is>
+      </c>
+      <c r="AI39" s="3" t="inlineStr">
+        <is>
+          <t>PAIR_038 | STRICT | Madiwala to Madhuravoyal</t>
+        </is>
+      </c>
+      <c r="AJ39" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-29_STAGE5_PRESERVE_CLASS_ISO_QC_V4_REGEX_FIX</t>
+        </is>
+      </c>
+      <c r="AK39" s="3" t="inlineStr">
+        <is>
+          <t>29-09-2026 12:15:35</t>
+        </is>
+      </c>
+      <c r="AL39" s="3" t="n">
+        <v>1247</v>
+      </c>
+      <c r="AM39" s="3" t="n">
+        <v>373</v>
+      </c>
+      <c r="AN39" s="3" t="n">
+        <v>9257.615000000002</v>
+      </c>
+      <c r="AO39" s="3" t="n">
+        <v>5393.673</v>
+      </c>
+      <c r="AP39" s="3" t="n">
+        <v>118652.8555237152</v>
+      </c>
+      <c r="AQ39" s="3" t="n">
+        <v>118320.5529638226</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AQ19"/>
+  <autoFilter ref="A1:AQ39"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>